--- a/Raspored.xlsx
+++ b/Raspored.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raspored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38F5BC6-8E70-4118-B7A8-E27C0FB311DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F8F702-B9DC-40A1-8405-511504A416D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E29FE33D-0FD8-4EFA-99F6-035E72B381D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E29FE33D-0FD8-4EFA-99F6-035E72B381D0}"/>
   </bookViews>
   <sheets>
     <sheet name="А смена" sheetId="2" r:id="rId1"/>
     <sheet name="Б смена" sheetId="1" r:id="rId2"/>
+    <sheet name="A смена допунска" sheetId="3" r:id="rId3"/>
+    <sheet name="Б смена допунска" sheetId="4" r:id="rId4"/>
+    <sheet name="A смена додатна" sheetId="5" r:id="rId5"/>
+    <sheet name="Б смена додатна" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="161">
   <si>
     <t>ПОНЕДЕЉАК</t>
   </si>
@@ -327,187 +331,202 @@
     <t>Грађанско</t>
   </si>
   <si>
+    <t>8/5 ч</t>
+  </si>
+  <si>
+    <t>6/3</t>
+  </si>
+  <si>
+    <t>6/2</t>
+  </si>
+  <si>
+    <t>5/2</t>
+  </si>
+  <si>
+    <t>5/1</t>
+  </si>
+  <si>
+    <t>6/3 ч</t>
+  </si>
+  <si>
+    <t>6/1</t>
+  </si>
+  <si>
+    <t>5/3</t>
+  </si>
+  <si>
+    <t>5/3 ч</t>
+  </si>
+  <si>
+    <t>6/2 ч</t>
+  </si>
+  <si>
+    <t>Иван Ловрић</t>
+  </si>
+  <si>
+    <t>5/2 ч</t>
+  </si>
+  <si>
+    <t>8/3 ч</t>
+  </si>
+  <si>
+    <t>7/12</t>
+  </si>
+  <si>
+    <t>5/12</t>
+  </si>
+  <si>
+    <t>5/1 ч</t>
+  </si>
+  <si>
+    <t>6/12</t>
+  </si>
+  <si>
+    <t>6/14</t>
+  </si>
+  <si>
+    <t>8/123</t>
+  </si>
+  <si>
+    <t>6/23</t>
+  </si>
+  <si>
+    <t>5/23</t>
+  </si>
+  <si>
+    <t>Зоран Шиљковић</t>
+  </si>
+  <si>
+    <t>7/1 ч</t>
+  </si>
+  <si>
+    <t>Слободан Перовић</t>
+  </si>
+  <si>
+    <t>7/13</t>
+  </si>
+  <si>
+    <t>6/1 ч</t>
+  </si>
+  <si>
+    <t>Милан Шиљеговић</t>
+  </si>
+  <si>
+    <t>6/4 ч</t>
+  </si>
+  <si>
+    <t>7/23</t>
+  </si>
+  <si>
+    <t>8/23</t>
+  </si>
+  <si>
+    <t>6/24</t>
+  </si>
+  <si>
+    <t>6/13</t>
+  </si>
+  <si>
+    <t>5/4</t>
+  </si>
+  <si>
+    <t>6/5 ч</t>
+  </si>
+  <si>
+    <t>7/7</t>
+  </si>
+  <si>
+    <t>5/6 ч</t>
+  </si>
+  <si>
+    <t>8/45</t>
+  </si>
+  <si>
+    <t>7/67</t>
+  </si>
+  <si>
+    <t>5/467</t>
+  </si>
+  <si>
+    <t>7/45</t>
+  </si>
+  <si>
+    <t>6/56</t>
+  </si>
+  <si>
+    <t>5/5 ч</t>
+  </si>
+  <si>
+    <t>7/7 ч</t>
+  </si>
+  <si>
+    <t>5/4 ч</t>
+  </si>
+  <si>
+    <t>5/67</t>
+  </si>
+  <si>
+    <t>5/45</t>
+  </si>
+  <si>
+    <t>8/6 ч</t>
+  </si>
+  <si>
+    <t>Жарко Гојковић</t>
+  </si>
+  <si>
+    <t>8/46</t>
+  </si>
+  <si>
+    <t>6/57</t>
+  </si>
+  <si>
+    <t>Ивана Пауновић Марковић</t>
+  </si>
+  <si>
+    <t>5/46</t>
+  </si>
+  <si>
+    <t>5/57</t>
+  </si>
+  <si>
+    <t>Гордана Вукчевић</t>
+  </si>
+  <si>
+    <t>Ана Делић</t>
+  </si>
+  <si>
+    <t>8/2 ч</t>
+  </si>
+  <si>
+    <t>7/2 ч</t>
+  </si>
+  <si>
+    <t>8/1 ч</t>
+  </si>
+  <si>
+    <t>7/3 ч</t>
+  </si>
+  <si>
     <t>ОВ</t>
   </si>
   <si>
-    <t>8/5 ч</t>
-  </si>
-  <si>
-    <t>6/3</t>
-  </si>
-  <si>
-    <t>6/2</t>
-  </si>
-  <si>
-    <t>5/2</t>
-  </si>
-  <si>
-    <t>5/1</t>
-  </si>
-  <si>
-    <t>6/3 ч</t>
-  </si>
-  <si>
-    <t>6/1</t>
-  </si>
-  <si>
-    <t>5/3</t>
-  </si>
-  <si>
-    <t>5/3 ч</t>
-  </si>
-  <si>
-    <t>6/2 ч</t>
-  </si>
-  <si>
-    <t>Иван Ловрић</t>
-  </si>
-  <si>
-    <t>5/2 ч</t>
-  </si>
-  <si>
-    <t>8/3 ч</t>
-  </si>
-  <si>
-    <t>7/12</t>
-  </si>
-  <si>
-    <t>5/12</t>
-  </si>
-  <si>
-    <t>5/1 ч</t>
-  </si>
-  <si>
-    <t>6/12</t>
-  </si>
-  <si>
-    <t>6/14</t>
-  </si>
-  <si>
-    <t>8/123</t>
-  </si>
-  <si>
-    <t>6/23</t>
-  </si>
-  <si>
-    <t>5/23</t>
-  </si>
-  <si>
-    <t>Зоран Шиљковић</t>
-  </si>
-  <si>
-    <t>7/1 ч</t>
-  </si>
-  <si>
-    <t>Слободан Перовић</t>
-  </si>
-  <si>
-    <t>7/13</t>
-  </si>
-  <si>
-    <t>6/1 ч</t>
-  </si>
-  <si>
-    <t>Милан Шиљеговић</t>
-  </si>
-  <si>
-    <t>6/4 ч</t>
-  </si>
-  <si>
-    <t>Марина Илијевски</t>
-  </si>
-  <si>
-    <t>7/23</t>
-  </si>
-  <si>
-    <t>8/23</t>
-  </si>
-  <si>
-    <t>6/24</t>
-  </si>
-  <si>
-    <t>6/13</t>
-  </si>
-  <si>
-    <t>5/4</t>
-  </si>
-  <si>
-    <t>6/5 ч</t>
-  </si>
-  <si>
-    <t>7/7</t>
-  </si>
-  <si>
-    <t>5/6 ч</t>
-  </si>
-  <si>
-    <t>8/45</t>
-  </si>
-  <si>
-    <t>7/67</t>
-  </si>
-  <si>
-    <t>5/467</t>
-  </si>
-  <si>
-    <t>7/45</t>
-  </si>
-  <si>
-    <t>6/56</t>
-  </si>
-  <si>
-    <t>5/5 ч</t>
-  </si>
-  <si>
-    <t>7/7 ч</t>
-  </si>
-  <si>
-    <t>5/4 ч</t>
-  </si>
-  <si>
-    <t>5/67</t>
-  </si>
-  <si>
-    <t>5/45</t>
-  </si>
-  <si>
-    <t>8/6 ч</t>
-  </si>
-  <si>
-    <t>Жарко Гојковић</t>
-  </si>
-  <si>
-    <t>8/46</t>
-  </si>
-  <si>
-    <t>6/57</t>
-  </si>
-  <si>
-    <t>Ивана Пауновић Марковић</t>
-  </si>
-  <si>
-    <t>5/46</t>
-  </si>
-  <si>
-    <t>5/57</t>
-  </si>
-  <si>
-    <t>Гордана Вукчевић</t>
-  </si>
-  <si>
-    <t>Ана Делић</t>
-  </si>
-  <si>
-    <t>8/2 ч</t>
-  </si>
-  <si>
-    <t>7/2 ч</t>
-  </si>
-  <si>
-    <t>8/1 ч</t>
-  </si>
-  <si>
-    <t>7/3 ч</t>
+    <t>7/6 ч</t>
+  </si>
+  <si>
+    <t>8/4 ч</t>
+  </si>
+  <si>
+    <t>7/5 ч</t>
+  </si>
+  <si>
+    <t>6/7 ч</t>
+  </si>
+  <si>
+    <t>7/4 ч</t>
+  </si>
+  <si>
+    <t>6/6 ч</t>
   </si>
 </sst>
 </file>
@@ -733,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -822,6 +841,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -829,6 +851,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1183,51 +1211,51 @@
       <c r="B1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="29" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="29" t="s">
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="29" t="s">
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="29" t="s">
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="32"/>
     </row>
     <row r="2" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3"/>
@@ -1345,74 +1373,74 @@
         <v>52</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="L3" s="11"/>
       <c r="M3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="O3" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="P3" s="12"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S3" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T3" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="12"/>
       <c r="X3" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Y3" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z3" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AF3" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG3" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="AG3" s="11" t="s">
-        <v>99</v>
-      </c>
       <c r="AH3" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AI3" s="11"/>
       <c r="AJ3" s="11"/>
@@ -1445,17 +1473,17 @@
       <c r="J4" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="14"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="14"/>
@@ -1478,7 +1506,7 @@
       </c>
       <c r="Z4" s="14"/>
       <c r="AA4" s="14" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AB4" s="14" t="s">
         <v>75</v>
@@ -1508,16 +1536,16 @@
         <v>78</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" s="14" t="s">
         <v>72</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>34</v>
@@ -1528,23 +1556,23 @@
       <c r="J5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="M5" s="32" t="s">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="M5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="O5" s="32"/>
+      <c r="N5" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="14"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="R5" s="14" t="s">
-        <v>103</v>
       </c>
       <c r="S5" s="14"/>
       <c r="T5" s="14" t="s">
@@ -1554,7 +1582,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="W5" s="15"/>
       <c r="X5" s="13"/>
@@ -1562,17 +1590,17 @@
       <c r="Z5" s="14"/>
       <c r="AA5" s="14"/>
       <c r="AB5" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC5" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="AC5" s="14" t="s">
-        <v>103</v>
       </c>
       <c r="AD5" s="15"/>
       <c r="AE5" s="13"/>
       <c r="AF5" s="14"/>
       <c r="AG5" s="14"/>
       <c r="AH5" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AI5" s="14" t="s">
         <v>34</v>
@@ -1587,7 +1615,7 @@
         <v>94</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1597,11 +1625,11 @@
       <c r="H6" s="14"/>
       <c r="I6" s="15"/>
       <c r="J6" s="13"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="13"/>
       <c r="R6" s="14"/>
@@ -1614,7 +1642,7 @@
       <c r="Y6" s="14"/>
       <c r="Z6" s="14"/>
       <c r="AA6" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AB6" s="14"/>
       <c r="AC6" s="14"/>
@@ -1639,34 +1667,34 @@
       <c r="E7" s="14"/>
       <c r="F7" s="14"/>
       <c r="G7" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>74</v>
       </c>
       <c r="I7" s="15"/>
       <c r="J7" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="M7" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32" t="s">
-        <v>103</v>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="P7" s="15"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="14"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="U7" s="14" t="s">
         <v>76</v>
@@ -1676,7 +1704,7 @@
       </c>
       <c r="W7" s="15"/>
       <c r="X7" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Y7" s="14" t="s">
         <v>73</v>
@@ -1693,7 +1721,7 @@
       <c r="AC7" s="14"/>
       <c r="AD7" s="15"/>
       <c r="AE7" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AF7" s="14" t="s">
         <v>76</v>
@@ -1718,26 +1746,26 @@
         <v>34</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
       <c r="I8" s="15"/>
       <c r="J8" s="13"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
       <c r="P8" s="15"/>
       <c r="Q8" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="R8" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="R8" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>34</v>
@@ -1758,7 +1786,7 @@
       <c r="AG8" s="14"/>
       <c r="AH8" s="14"/>
       <c r="AI8" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AJ8" s="14"/>
       <c r="AK8" s="15"/>
@@ -1768,10 +1796,10 @@
         <v>79</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
@@ -1780,11 +1808,11 @@
       <c r="H9" s="14"/>
       <c r="I9" s="15"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="14"/>
@@ -1804,11 +1832,11 @@
       <c r="AF9" s="14"/>
       <c r="AG9" s="14"/>
       <c r="AH9" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AI9" s="14"/>
       <c r="AJ9" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AK9" s="15"/>
     </row>
@@ -1824,36 +1852,36 @@
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="13"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="13" t="s">
         <v>74</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S10" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T10" s="14"/>
       <c r="U10" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="V10" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="V10" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="W10" s="15" t="s">
         <v>75</v>
@@ -1869,13 +1897,13 @@
         <v>75</v>
       </c>
       <c r="AF10" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG10" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AH10" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI10" s="14"/>
       <c r="AJ10" s="14"/>
@@ -1898,15 +1926,15 @@
         <v>34</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="32"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="13" t="s">
         <v>76</v>
@@ -1915,7 +1943,7 @@
         <v>34</v>
       </c>
       <c r="S11" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T11" s="14"/>
       <c r="U11" s="14" t="s">
@@ -1934,10 +1962,10 @@
         <v>76</v>
       </c>
       <c r="AF11" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG11" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH11" s="14"/>
       <c r="AI11" s="14"/>
@@ -1958,34 +1986,34 @@
         <v>73</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="32"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
       <c r="P12" s="15"/>
       <c r="Q12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="R12" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="S12" s="14" t="s">
         <v>114</v>
-      </c>
-      <c r="R12" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="S12" s="14" t="s">
-        <v>115</v>
       </c>
       <c r="T12" s="14"/>
       <c r="U12" s="14" t="s">
         <v>73</v>
       </c>
       <c r="V12" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W12" s="15"/>
       <c r="X12" s="13"/>
@@ -1996,19 +2024,19 @@
       <c r="AC12" s="14"/>
       <c r="AD12" s="15"/>
       <c r="AE12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF12" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG12" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="AF12" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG12" s="14" t="s">
-        <v>115</v>
-      </c>
       <c r="AH12" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI12" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AJ12" s="14"/>
       <c r="AK12" s="15"/>
@@ -2026,15 +2054,15 @@
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
       <c r="P13" s="15"/>
       <c r="Q13" s="13"/>
       <c r="R13" s="14"/>
@@ -2052,7 +2080,7 @@
       <c r="AD13" s="15"/>
       <c r="AE13" s="13"/>
       <c r="AF13" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG13" s="14"/>
       <c r="AH13" s="14"/>
@@ -2065,81 +2093,81 @@
         <v>82</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="15"/>
       <c r="J14" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="32"/>
+        <v>97</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
+      <c r="O14" s="14"/>
       <c r="P14" s="15"/>
       <c r="Q14" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="R14" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="S14" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="T14" s="14" t="s">
         <v>98</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="T14" s="14" t="s">
-        <v>99</v>
       </c>
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="15"/>
       <c r="X14" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y14" s="14"/>
       <c r="Z14" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AA14" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AB14" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AC14" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AD14" s="15"/>
       <c r="AE14" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AF14" s="14"/>
       <c r="AG14" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AH14" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI14" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="AI14" s="14" t="s">
-        <v>99</v>
-      </c>
       <c r="AJ14" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AK14" s="15"/>
     </row>
@@ -2170,17 +2198,17 @@
       <c r="J15" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="K15" s="32" t="s">
+      <c r="K15" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="32" t="s">
+      <c r="L15" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="M15" s="32" t="s">
+      <c r="M15" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="13" t="s">
         <v>71</v>
@@ -2224,7 +2252,7 @@
         <v>76</v>
       </c>
       <c r="AJ15" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK15" s="15"/>
     </row>
@@ -2239,33 +2267,33 @@
         <v>75</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
       <c r="I16" s="15"/>
       <c r="J16" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="K16" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="L16" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="M16" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="N16" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="O16" s="32"/>
+      <c r="O16" s="14"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="13"/>
       <c r="R16" s="14"/>
@@ -2278,7 +2306,7 @@
         <v>75</v>
       </c>
       <c r="Y16" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Z16" s="14" t="s">
         <v>34</v>
@@ -2310,15 +2338,15 @@
       <c r="H17" s="14"/>
       <c r="I17" s="15"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32" t="s">
+      <c r="K17" s="14"/>
+      <c r="L17" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32" t="s">
+      <c r="M17" s="14"/>
+      <c r="N17" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="O17" s="32" t="s">
+      <c r="O17" s="14" t="s">
         <v>75</v>
       </c>
       <c r="P17" s="15"/>
@@ -2355,7 +2383,7 @@
         <v>84</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -2367,13 +2395,13 @@
       <c r="J18" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="32" t="s">
+      <c r="K18" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="14"/>
@@ -2424,19 +2452,19 @@
       <c r="J19" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="L19" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="M19" s="32" t="s">
+      <c r="K19" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="N19" s="32" t="s">
+      <c r="M19" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="O19" s="32"/>
+      <c r="O19" s="14"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="13" t="s">
         <v>73</v>
@@ -2445,7 +2473,7 @@
         <v>72</v>
       </c>
       <c r="S19" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T19" s="14"/>
       <c r="U19" s="14" t="s">
@@ -2456,13 +2484,13 @@
       </c>
       <c r="W19" s="15"/>
       <c r="X19" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Y19" s="14" t="s">
         <v>74</v>
       </c>
       <c r="Z19" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AA19" s="14"/>
       <c r="AB19" s="14" t="s">
@@ -2476,7 +2504,7 @@
         <v>72</v>
       </c>
       <c r="AF19" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AG19" s="14" t="s">
         <v>34</v>
@@ -2501,11 +2529,11 @@
       <c r="H20" s="14"/>
       <c r="I20" s="15"/>
       <c r="J20" s="13"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="14"/>
@@ -2554,22 +2582,22 @@
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="13"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32" t="s">
+      <c r="K21" s="14"/>
+      <c r="L21" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="M21" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="M21" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="N21" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="O21" s="32" t="s">
+      <c r="O21" s="14" t="s">
         <v>34</v>
       </c>
       <c r="P21" s="15"/>
       <c r="Q21" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R21" s="14" t="s">
         <v>76</v>
@@ -2585,7 +2613,7 @@
         <v>34</v>
       </c>
       <c r="Y21" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Z21" s="14" t="s">
         <v>71</v>
@@ -2599,13 +2627,13 @@
       </c>
       <c r="AD21" s="15"/>
       <c r="AE21" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AF21" s="14" t="s">
         <v>75</v>
       </c>
       <c r="AG21" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AH21" s="14"/>
       <c r="AI21" s="14" t="s">
@@ -2624,36 +2652,36 @@
         <v>20</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D22" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>99</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>100</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="15"/>
       <c r="J22" s="13"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="13"/>
       <c r="R22" s="14"/>
       <c r="S22" s="14"/>
       <c r="T22" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U22" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="V22" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W22" s="15"/>
       <c r="X22" s="13"/>
@@ -2680,10 +2708,10 @@
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>75</v>
@@ -2696,16 +2724,16 @@
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="13"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32" t="s">
+      <c r="K23" s="14"/>
+      <c r="L23" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32" t="s">
+      <c r="M23" s="14"/>
+      <c r="N23" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="O23" s="32" t="s">
-        <v>102</v>
+      <c r="O23" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="P23" s="15"/>
       <c r="Q23" s="13" t="s">
@@ -2719,20 +2747,20 @@
         <v>76</v>
       </c>
       <c r="U23" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V23" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="W23" s="15"/>
       <c r="X23" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Y23" s="14" t="s">
         <v>34</v>
       </c>
       <c r="Z23" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA23" s="14"/>
       <c r="AB23" s="14"/>
@@ -2771,17 +2799,17 @@
       <c r="H24" s="14"/>
       <c r="I24" s="15"/>
       <c r="J24" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M24" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="M24" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="14"/>
@@ -2820,14 +2848,14 @@
       <c r="H25" s="14"/>
       <c r="I25" s="15"/>
       <c r="J25" s="13"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="32" t="s">
-        <v>120</v>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="P25" s="15" t="s">
         <v>76</v>
@@ -2842,14 +2870,14 @@
       <c r="X25" s="13"/>
       <c r="Y25" s="14"/>
       <c r="Z25" s="14"/>
-      <c r="AA25" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB25" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="AC25" s="32" t="s">
-        <v>128</v>
+      <c r="AA25" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB25" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC25" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="AD25" s="15"/>
       <c r="AE25" s="13"/>
@@ -2877,24 +2905,24 @@
         <v>71</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I26" s="15"/>
       <c r="J26" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32" t="s">
+      <c r="L26" s="14"/>
+      <c r="M26" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="N26" s="32" t="s">
+      <c r="N26" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="O26" s="32" t="s">
-        <v>98</v>
+      <c r="O26" s="14" t="s">
+        <v>97</v>
       </c>
       <c r="P26" s="15"/>
       <c r="Q26" s="13"/>
@@ -2902,7 +2930,7 @@
         <v>74</v>
       </c>
       <c r="S26" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T26" s="14" t="s">
         <v>75</v>
@@ -2913,10 +2941,10 @@
       <c r="V26" s="14"/>
       <c r="W26" s="15"/>
       <c r="X26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y26" s="14" t="s">
         <v>97</v>
-      </c>
-      <c r="Y26" s="14" t="s">
-        <v>98</v>
       </c>
       <c r="Z26" s="14" t="s">
         <v>72</v>
@@ -2936,7 +2964,7 @@
         <v>75</v>
       </c>
       <c r="AI26" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AJ26" s="14" t="s">
         <v>34</v>
@@ -2951,24 +2979,24 @@
         <v>62</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F27" s="14"/>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15"/>
       <c r="J27" s="13"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="14"/>
@@ -3005,7 +3033,7 @@
         <v>75</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14" t="s">
@@ -3015,20 +3043,20 @@
         <v>72</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="K28" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="N28" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="O28" s="32" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="O28" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="13"/>
@@ -3068,11 +3096,11 @@
       <c r="H29" s="14"/>
       <c r="I29" s="15"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
@@ -3089,13 +3117,13 @@
         <v>71</v>
       </c>
       <c r="Y29" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Z29" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AA29" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AB29" s="14"/>
       <c r="AC29" s="14" t="s">
@@ -3122,27 +3150,27 @@
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
       <c r="G30" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>72</v>
       </c>
       <c r="I30" s="15"/>
       <c r="J30" s="13"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32" t="s">
+      <c r="K30" s="14"/>
+      <c r="L30" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="O30" s="32" t="s">
-        <v>99</v>
+      <c r="O30" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="P30" s="15"/>
       <c r="Q30" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R30" s="14"/>
       <c r="S30" s="14" t="s">
@@ -3157,16 +3185,16 @@
       <c r="X30" s="13"/>
       <c r="Y30" s="14"/>
       <c r="Z30" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AA30" s="14" t="s">
         <v>34</v>
       </c>
       <c r="AB30" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AC30" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AD30" s="15"/>
       <c r="AE30" s="13"/>
@@ -3178,10 +3206,10 @@
         <v>73</v>
       </c>
       <c r="AI30" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AJ30" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AK30" s="15"/>
     </row>
@@ -3208,17 +3236,17 @@
       <c r="J31" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32" t="s">
+      <c r="K31" s="14"/>
+      <c r="L31" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="M31" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="N31" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="O31" s="32"/>
+      <c r="M31" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="O31" s="14"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="13" t="s">
         <v>34</v>
@@ -3233,10 +3261,10 @@
         <v>72</v>
       </c>
       <c r="U31" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V31" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W31" s="15"/>
       <c r="X31" s="13"/>
@@ -3244,7 +3272,7 @@
       <c r="Z31" s="14"/>
       <c r="AA31" s="14"/>
       <c r="AB31" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AC31" s="14" t="s">
         <v>72</v>
@@ -3260,10 +3288,10 @@
       </c>
       <c r="AI31" s="14"/>
       <c r="AJ31" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK31" s="15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3283,23 +3311,23 @@
         <v>76</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="N32" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="O32" s="32" t="s">
+      <c r="K32" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="O32" s="14" t="s">
         <v>74</v>
       </c>
       <c r="P32" s="15"/>
@@ -3308,10 +3336,10 @@
       <c r="S32" s="14"/>
       <c r="T32" s="14"/>
       <c r="U32" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V32" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="W32" s="15" t="s">
         <v>74</v>
@@ -3320,34 +3348,34 @@
         <v>73</v>
       </c>
       <c r="Y32" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Z32" s="14" t="s">
         <v>76</v>
       </c>
       <c r="AA32" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AB32" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AC32" s="14"/>
       <c r="AD32" s="15"/>
       <c r="AE32" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF32" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG32" s="14" t="s">
         <v>76</v>
       </c>
       <c r="AH32" s="14"/>
       <c r="AI32" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AJ32" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AK32" s="15" t="s">
         <v>73</v>
@@ -3372,37 +3400,37 @@
       <c r="H33" s="14"/>
       <c r="I33" s="15"/>
       <c r="J33" s="13"/>
-      <c r="K33" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="L33" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32" t="s">
+      <c r="K33" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="O33" s="32" t="s">
+      <c r="O33" s="14" t="s">
         <v>76</v>
       </c>
       <c r="P33" s="15"/>
       <c r="Q33" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R33" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S33" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U33" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V33" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W33" s="15"/>
       <c r="X33" s="13"/>
@@ -3423,10 +3451,10 @@
       <c r="AE33" s="13"/>
       <c r="AF33" s="14"/>
       <c r="AG33" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH33" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AI33" s="14" t="s">
         <v>74</v>
@@ -3441,7 +3469,7 @@
         <v>91</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>71</v>
@@ -3456,40 +3484,40 @@
         <v>72</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I34" s="15"/>
       <c r="J34" s="13"/>
-      <c r="K34" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="L34" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32" t="s">
+      <c r="K34" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="O34" s="32" t="s">
+      <c r="O34" s="14" t="s">
         <v>76</v>
       </c>
       <c r="P34" s="15"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="14"/>
       <c r="S34" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="U34" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V34" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="W34" s="15"/>
       <c r="X34" s="13"/>
@@ -3524,10 +3552,10 @@
         <v>91</v>
       </c>
       <c r="B35" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="14" t="s">
         <v>122</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>123</v>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14" t="s">
@@ -3537,24 +3565,24 @@
         <v>72</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I35" s="15"/>
       <c r="J35" s="13"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R35" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="S35" s="14"/>
       <c r="T35" s="14"/>
@@ -3575,10 +3603,10 @@
         <v>34</v>
       </c>
       <c r="AG35" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AH35" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AI35" s="14" t="s">
         <v>74</v>
@@ -3600,29 +3628,29 @@
       <c r="E36" s="14"/>
       <c r="F36" s="14"/>
       <c r="G36" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>76</v>
       </c>
       <c r="J36" s="13"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="32"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
-      <c r="O36" s="32"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="13"/>
       <c r="R36" s="14"/>
       <c r="S36" s="14"/>
       <c r="T36" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U36" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V36" s="14" t="s">
         <v>34</v>
@@ -3638,14 +3666,14 @@
       <c r="AC36" s="14"/>
       <c r="AD36" s="15"/>
       <c r="AE36" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF36" s="14" t="s">
         <v>72</v>
       </c>
       <c r="AG36" s="14"/>
       <c r="AH36" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI36" s="14"/>
       <c r="AJ36" s="14"/>
@@ -3663,29 +3691,29 @@
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
       <c r="G37" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>76</v>
       </c>
       <c r="J37" s="13"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
-      <c r="O37" s="32"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="14"/>
       <c r="S37" s="14"/>
       <c r="T37" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="U37" s="14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="V37" s="14" t="s">
         <v>34</v>
@@ -3729,11 +3757,11 @@
       <c r="H38" s="14"/>
       <c r="I38" s="15"/>
       <c r="J38" s="13"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
-      <c r="M38" s="32"/>
-      <c r="N38" s="32"/>
-      <c r="O38" s="32"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="14"/>
@@ -3750,14 +3778,14 @@
       <c r="AC38" s="14"/>
       <c r="AD38" s="15"/>
       <c r="AE38" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AF38" s="14" t="s">
         <v>72</v>
       </c>
       <c r="AG38" s="14"/>
       <c r="AH38" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AI38" s="14" t="s">
         <v>75</v>
@@ -3784,17 +3812,17 @@
       <c r="H39" s="14"/>
       <c r="I39" s="15"/>
       <c r="J39" s="13"/>
-      <c r="K39" s="32" t="s">
+      <c r="K39" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32" t="s">
-        <v>125</v>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="P39" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="Q39" s="13"/>
       <c r="R39" s="14"/>
@@ -3807,13 +3835,13 @@
       <c r="Y39" s="14"/>
       <c r="Z39" s="14"/>
       <c r="AA39" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB39" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AC39" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AD39" s="15"/>
       <c r="AE39" s="13"/>
@@ -3839,11 +3867,11 @@
       <c r="H40" s="14"/>
       <c r="I40" s="15"/>
       <c r="J40" s="13"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="32"/>
-      <c r="N40" s="32"/>
-      <c r="O40" s="32"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
       <c r="P40" s="15"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="14"/>
@@ -3856,16 +3884,16 @@
       <c r="Y40" s="14"/>
       <c r="Z40" s="14"/>
       <c r="AA40" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AB40" s="14" t="s">
         <v>34</v>
       </c>
       <c r="AC40" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AD40" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AE40" s="13"/>
       <c r="AF40" s="14"/>
@@ -3895,7 +3923,7 @@
       <c r="M41" s="17"/>
       <c r="N41" s="17"/>
       <c r="O41" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P41" s="18" t="s">
         <v>75</v>
@@ -3953,51 +3981,51 @@
       <c r="B1" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="29" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="29" t="s">
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="29" t="s">
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="29" t="s">
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="32"/>
+      <c r="AE1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="32"/>
     </row>
     <row r="2" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="22"/>
@@ -4109,78 +4137,78 @@
       </c>
     </row>
     <row r="3" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="29" t="s">
         <v>78</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>45</v>
+      <c r="C3" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>38</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
       <c r="J3" s="10"/>
-      <c r="K3" s="11"/>
+      <c r="K3" s="11" t="s">
+        <v>45</v>
+      </c>
       <c r="L3" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>44</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="R3" s="11" t="s">
+      <c r="S3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="11" t="s">
-        <v>129</v>
-      </c>
       <c r="T3" s="11" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="12"/>
-      <c r="X3" s="10" t="s">
+      <c r="X3" s="10"/>
+      <c r="Y3" s="11"/>
+      <c r="Z3" s="11"/>
+      <c r="AA3" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB3" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="AC3" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="Y3" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA3" s="11"/>
-      <c r="AB3" s="11"/>
-      <c r="AC3" s="11"/>
       <c r="AD3" s="12"/>
       <c r="AE3" s="10"/>
-      <c r="AF3" s="11"/>
+      <c r="AF3" s="11" t="s">
+        <v>44</v>
+      </c>
       <c r="AG3" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH3" s="11"/>
+      <c r="AI3" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="AH3" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI3" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="AJ3" s="11" t="s">
         <v>38</v>
@@ -4194,80 +4222,80 @@
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="s">
+      <c r="G4" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="33"/>
+      <c r="L4" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" s="33" t="s">
         <v>50</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="14"/>
       <c r="S4" s="14" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="T4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="U4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="14" t="s">
-        <v>51</v>
-      </c>
       <c r="V4" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="W4" s="15"/>
       <c r="X4" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA4" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF4" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="14" t="s">
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="Z4" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="15"/>
-      <c r="AE4" s="13"/>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI4" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AJ4" s="14" t="s">
+      <c r="AJ4" s="33" t="s">
         <v>46</v>
       </c>
       <c r="AK4" s="15"/>
@@ -4279,25 +4307,27 @@
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
       <c r="I5" s="15"/>
       <c r="J5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="K5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="13" t="s">
         <v>43</v>
@@ -4311,26 +4341,24 @@
       <c r="V5" s="14"/>
       <c r="W5" s="15"/>
       <c r="X5" s="13"/>
-      <c r="Y5" s="14"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14" t="s">
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC5" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AC5" s="14" t="s">
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="33"/>
+      <c r="AH5" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="AD5" s="15"/>
-      <c r="AE5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG5" s="14"/>
-      <c r="AH5" s="14"/>
-      <c r="AI5" s="14"/>
-      <c r="AJ5" s="14"/>
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="33"/>
       <c r="AK5" s="15"/>
     </row>
     <row r="6" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4340,267 +4368,257 @@
       <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="14" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G6" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="33" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="15"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
+      <c r="J6" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
       <c r="P6" s="15"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14" t="s">
+      <c r="Q6" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="U6" s="14" t="s">
+      <c r="R6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="V6" s="14" t="s">
-        <v>131</v>
-      </c>
+      <c r="S6" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
       <c r="W6" s="15"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="14" t="s">
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="Z6" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC6" s="14" t="s">
-        <v>131</v>
+      <c r="AC6" s="33" t="s">
+        <v>130</v>
       </c>
       <c r="AD6" s="15"/>
       <c r="AE6" s="13"/>
-      <c r="AF6" s="14"/>
-      <c r="AG6" s="14"/>
-      <c r="AH6" s="14" t="s">
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" s="33"/>
+      <c r="AI6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="AI6" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AJ6" s="14" t="s">
-        <v>48</v>
+      <c r="AJ6" s="33" t="s">
+        <v>129</v>
       </c>
       <c r="AK6" s="15"/>
     </row>
     <row r="7" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="I7" s="15"/>
-      <c r="J7" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="M7" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="33"/>
       <c r="P7" s="15"/>
-      <c r="Q7" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="R7" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="14"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
       <c r="W7" s="15"/>
-      <c r="X7" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB7" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC7" s="14" t="s">
-        <v>37</v>
-      </c>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="33"/>
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="33"/>
       <c r="AD7" s="15"/>
-      <c r="AE7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF7" s="14" t="s">
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="33"/>
+      <c r="AH7" s="33"/>
+      <c r="AI7" s="33"/>
+      <c r="AJ7" s="33"/>
+      <c r="AK7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="AG7" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AH7" s="14"/>
-      <c r="AI7" s="14"/>
-      <c r="AJ7" s="14"/>
-      <c r="AK7" s="15"/>
     </row>
     <row r="8" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+        <v>8</v>
+      </c>
+      <c r="C8" s="13"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>46</v>
+      </c>
       <c r="I8" s="15"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="J8" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="33" t="s">
+        <v>38</v>
+      </c>
       <c r="P8" s="15"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="14"/>
-      <c r="S8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="T8" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="U8" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="V8" s="14" t="s">
-        <v>36</v>
-      </c>
+      <c r="Q8" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
       <c r="W8" s="15"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="14"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
+      <c r="X8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y8" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z8" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA8" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB8" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC8" s="33" t="s">
+        <v>47</v>
+      </c>
       <c r="AD8" s="15"/>
-      <c r="AE8" s="13"/>
-      <c r="AF8" s="14"/>
-      <c r="AG8" s="14"/>
-      <c r="AH8" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AJ8" s="14" t="s">
-        <v>44</v>
-      </c>
+      <c r="AE8" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF8" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AG8" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="33"/>
       <c r="AK8" s="15"/>
     </row>
     <row r="9" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
+        <v>9</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="33"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="33"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="14"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
+      <c r="S9" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="V9" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="W9" s="15"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="14"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB9" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC9" s="14" t="s">
-        <v>133</v>
-      </c>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="33"/>
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="33"/>
       <c r="AD9" s="15"/>
       <c r="AE9" s="13"/>
-      <c r="AF9" s="14"/>
-      <c r="AG9" s="14"/>
-      <c r="AH9" s="14"/>
-      <c r="AI9" s="14"/>
-      <c r="AJ9" s="14"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="33"/>
+      <c r="AH9" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI9" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ9" s="33" t="s">
+        <v>44</v>
+      </c>
       <c r="AK9" s="15"/>
     </row>
     <row r="10" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4608,29 +4626,27 @@
         <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>36</v>
-      </c>
+      <c r="J10" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="M10" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="14"/>
@@ -4639,27 +4655,25 @@
       <c r="U10" s="14"/>
       <c r="V10" s="14"/>
       <c r="W10" s="15"/>
-      <c r="X10" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y10" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA10" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB10" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC10" s="33" t="s">
+        <v>131</v>
+      </c>
       <c r="AD10" s="15"/>
       <c r="AE10" s="13"/>
-      <c r="AF10" s="14"/>
-      <c r="AG10" s="14"/>
-      <c r="AH10" s="14"/>
-      <c r="AI10" s="14"/>
-      <c r="AJ10" s="14"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="33"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="33"/>
+      <c r="AJ10" s="33"/>
       <c r="AK10" s="15"/>
     </row>
     <row r="11" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4667,26 +4681,28 @@
         <v>80</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
+        <v>11</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
       <c r="I11" s="15"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>137</v>
+      <c r="K11" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" s="33" t="s">
+        <v>36</v>
       </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="13"/>
@@ -4697,51 +4713,53 @@
       <c r="V11" s="14"/>
       <c r="W11" s="15"/>
       <c r="X11" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA11" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="Y11" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z11" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA11" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
       <c r="AD11" s="15"/>
       <c r="AE11" s="13"/>
-      <c r="AF11" s="14"/>
-      <c r="AG11" s="14"/>
-      <c r="AH11" s="14"/>
-      <c r="AI11" s="14"/>
-      <c r="AJ11" s="14"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
       <c r="AK11" s="15"/>
     </row>
     <row r="12" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
+        <v>80</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
       <c r="I12" s="15"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="M12" s="14" t="s">
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="O12" s="33" t="s">
         <v>135</v>
-      </c>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14" t="s">
-        <v>69</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="13"/>
@@ -4751,25 +4769,25 @@
       <c r="U12" s="14"/>
       <c r="V12" s="14"/>
       <c r="W12" s="15"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="14"/>
-      <c r="Z12" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="AA12" s="14" t="s">
+      <c r="X12" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="AB12" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC12" s="14"/>
+      <c r="AA12" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="33"/>
       <c r="AD12" s="15"/>
       <c r="AE12" s="13"/>
-      <c r="AF12" s="14"/>
-      <c r="AG12" s="14"/>
-      <c r="AH12" s="14"/>
-      <c r="AI12" s="14"/>
-      <c r="AJ12" s="14"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="33"/>
+      <c r="AH12" s="33"/>
+      <c r="AI12" s="33"/>
+      <c r="AJ12" s="33"/>
       <c r="AK12" s="15"/>
     </row>
     <row r="13" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4777,32 +4795,26 @@
         <v>81</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
+        <v>13</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="13"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="M13" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>47</v>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="13"/>
@@ -4812,114 +4824,90 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="15"/>
-      <c r="X13" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z13" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14" t="s">
+      <c r="X13" s="13"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA13" s="33" t="s">
         <v>133</v>
       </c>
+      <c r="AB13" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC13" s="33"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="13"/>
-      <c r="AF13" s="14"/>
-      <c r="AG13" s="14"/>
-      <c r="AH13" s="14"/>
-      <c r="AI13" s="14"/>
-      <c r="AJ13" s="14"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="33"/>
+      <c r="AH13" s="33"/>
+      <c r="AI13" s="33"/>
+      <c r="AJ13" s="33"/>
       <c r="AK13" s="15"/>
     </row>
     <row r="14" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="14"/>
+        <v>39</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
       <c r="I14" s="15"/>
       <c r="J14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
+      <c r="N14" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="O14" s="33" t="s">
+        <v>47</v>
+      </c>
       <c r="P14" s="15"/>
-      <c r="Q14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="S14" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="14"/>
+      <c r="S14" s="14"/>
       <c r="T14" s="14"/>
-      <c r="U14" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="15"/>
       <c r="X14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z14" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z14" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA14" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AA14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
+      <c r="AB14" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC14" s="33" t="s">
+        <v>131</v>
+      </c>
       <c r="AD14" s="15"/>
-      <c r="AE14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG14" s="14"/>
-      <c r="AH14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI14" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ14" s="14" t="s">
-        <v>96</v>
-      </c>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="33"/>
+      <c r="AH14" s="33"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="33"/>
       <c r="AK14" s="15"/>
     </row>
     <row r="15" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4927,84 +4915,84 @@
         <v>82</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>139</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
       <c r="I15" s="15"/>
       <c r="J15" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="N15" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="M15" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" s="33"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R15" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S15" s="14" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="U15" s="14" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="V15" s="14"/>
       <c r="W15" s="15"/>
       <c r="X15" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y15" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="Z15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
+        <v>45</v>
+      </c>
+      <c r="Y15" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z15" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA15" s="33"/>
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
       <c r="AD15" s="15"/>
       <c r="AE15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG15" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AI15" s="14"/>
-      <c r="AJ15" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH15" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI15" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ15" s="33" t="s">
+        <v>95</v>
+      </c>
       <c r="AK15" s="15"/>
     </row>
     <row r="16" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5012,58 +5000,84 @@
         <v>82</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>137</v>
+      </c>
       <c r="I16" s="15"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
+      <c r="J16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="M16" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" s="14"/>
+        <v>47</v>
+      </c>
+      <c r="S16" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="T16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="U16" s="14"/>
+        <v>129</v>
+      </c>
+      <c r="U16" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="V16" s="14"/>
       <c r="W16" s="15"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
+      <c r="X16" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y16" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
       <c r="AD16" s="15"/>
-      <c r="AE16" s="13"/>
-      <c r="AF16" s="14"/>
-      <c r="AG16" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI16" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AJ16" s="14"/>
+      <c r="AE16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF16" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG16" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH16" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="33"/>
       <c r="AK16" s="15"/>
     </row>
     <row r="17" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5071,301 +5085,275 @@
         <v>82</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="33"/>
       <c r="I17" s="15"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
       <c r="P17" s="15"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
+      <c r="Q17" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="U17" s="14"/>
       <c r="V17" s="14"/>
       <c r="W17" s="15"/>
-      <c r="X17" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z17" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF17" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG17" s="14"/>
-      <c r="AH17" s="14"/>
-      <c r="AI17" s="14"/>
-      <c r="AJ17" s="14"/>
+      <c r="AE17" s="13"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ17" s="33"/>
       <c r="AK17" s="15"/>
     </row>
     <row r="18" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D18" s="33" t="s">
         <v>51</v>
       </c>
+      <c r="E18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
       <c r="I18" s="15"/>
-      <c r="J18" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
       <c r="P18" s="15"/>
-      <c r="Q18" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R18" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="S18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="T18" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="U18" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="V18" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
       <c r="W18" s="15"/>
       <c r="X18" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y18" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z18" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA18" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB18" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC18" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="Y18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z18" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
       <c r="AD18" s="15"/>
       <c r="AE18" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF18" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AG18" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH18" s="14"/>
-      <c r="AI18" s="14"/>
-      <c r="AJ18" s="14"/>
+        <v>127</v>
+      </c>
+      <c r="AF18" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG18" s="33"/>
+      <c r="AH18" s="33"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="33"/>
       <c r="AK18" s="15"/>
     </row>
     <row r="19" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14" t="s">
+      <c r="H19" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
+      <c r="K19" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="T19" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="U19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="V19" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="W19" s="15"/>
+      <c r="X19" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y19" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z19" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="R19" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S19" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="T19" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="U19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="V19" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="W19" s="15"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="33"/>
       <c r="AD19" s="15"/>
       <c r="AE19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF19" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG19" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH19" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="AF19" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG19" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH19" s="14"/>
-      <c r="AI19" s="14"/>
-      <c r="AJ19" s="14"/>
+      <c r="AI19" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ19" s="33"/>
       <c r="AK19" s="15"/>
     </row>
     <row r="20" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="F20" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="H20" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
       <c r="I20" s="15"/>
-      <c r="J20" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="M20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N20" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="O20" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="J20" s="13"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="13"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14" t="s">
-        <v>44</v>
-      </c>
+      <c r="R20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S20" s="14"/>
       <c r="T20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="U20" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="U20" s="14" t="s">
+      <c r="V20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="V20" s="14" t="s">
-        <v>43</v>
-      </c>
       <c r="W20" s="15"/>
-      <c r="X20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y20" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB20" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC20" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="33"/>
       <c r="AD20" s="15"/>
       <c r="AE20" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF20" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="AF20" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG20" s="14"/>
-      <c r="AH20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI20" s="14"/>
-      <c r="AJ20" s="14"/>
+      <c r="AG20" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AH20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI20" s="33"/>
+      <c r="AJ20" s="33"/>
       <c r="AK20" s="15"/>
     </row>
     <row r="21" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5373,143 +5361,143 @@
         <v>85</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>45</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
       <c r="I21" s="15"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
+      <c r="J21" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K21" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="M21" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="N21" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="O21" s="33" t="s">
+        <v>35</v>
+      </c>
       <c r="P21" s="15"/>
-      <c r="Q21" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="14"/>
       <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
+      <c r="T21" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="U21" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="V21" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="W21" s="15"/>
-      <c r="X21" s="13"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
+      <c r="X21" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y21" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB21" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC21" s="33" t="s">
+        <v>43</v>
+      </c>
       <c r="AD21" s="15"/>
-      <c r="AE21" s="13"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AH21" s="14"/>
-      <c r="AI21" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ21" s="14" t="s">
-        <v>37</v>
-      </c>
+      <c r="AE21" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF21" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG21" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH21" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="33"/>
       <c r="AK21" s="15"/>
     </row>
     <row r="22" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="H22" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33" t="s">
         <v>37</v>
       </c>
+      <c r="G22" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="I22" s="15"/>
-      <c r="J22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O22" s="14"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R22" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="S22" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="R22" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="S22" s="14" t="s">
-        <v>131</v>
       </c>
       <c r="T22" s="14"/>
       <c r="U22" s="14"/>
       <c r="V22" s="14"/>
       <c r="W22" s="15"/>
-      <c r="X22" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y22" s="14" t="s">
+      <c r="X22" s="13"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="15"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="33"/>
+      <c r="AH22" s="33"/>
+      <c r="AI22" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ22" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="Z22" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC22" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF22" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG22" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH22" s="14"/>
-      <c r="AI22" s="14"/>
-      <c r="AJ22" s="14"/>
       <c r="AK22" s="15"/>
     </row>
     <row r="23" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5517,282 +5505,310 @@
         <v>86</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>44</v>
+      </c>
       <c r="I23" s="15"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
+      <c r="J23" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L23" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="O23" s="33" t="s">
+        <v>159</v>
+      </c>
       <c r="P23" s="15"/>
-      <c r="Q23" s="13"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="U23" s="14" t="s">
-        <v>129</v>
-      </c>
+      <c r="Q23" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S23" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="15"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
+      <c r="X23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y23" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z23" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC23" s="33" t="s">
+        <v>50</v>
+      </c>
       <c r="AD23" s="15"/>
-      <c r="AE23" s="13"/>
-      <c r="AF23" s="14"/>
-      <c r="AG23" s="14"/>
-      <c r="AH23" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI23" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ23" s="14"/>
+      <c r="AE23" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF23" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG23" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH23" s="33"/>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="33"/>
       <c r="AK23" s="15"/>
     </row>
-    <row r="24" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="33"/>
       <c r="I24" s="15"/>
       <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="13"/>
-      <c r="R24" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="S24" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="T24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="U24" s="14"/>
-      <c r="V24" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="W24" s="15" t="s">
-        <v>134</v>
-      </c>
+      <c r="V24" s="14"/>
+      <c r="W24" s="15"/>
       <c r="X24" s="13"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
       <c r="AD24" s="15"/>
       <c r="AE24" s="13"/>
-      <c r="AF24" s="14"/>
-      <c r="AG24" s="14"/>
-      <c r="AH24" s="14"/>
-      <c r="AI24" s="14"/>
-      <c r="AJ24" s="14"/>
-      <c r="AK24" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="33"/>
+      <c r="AH24" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI24" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ24" s="33"/>
+      <c r="AK24" s="15"/>
+    </row>
+    <row r="25" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="O25" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="I25" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J25" s="13"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
       <c r="P25" s="15"/>
-      <c r="Q25" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="R25" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="17"/>
       <c r="T25" s="14"/>
       <c r="U25" s="14" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="V25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="W25" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="W25" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="X25" s="13"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA25" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB25" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC25" s="14" t="s">
-        <v>44</v>
-      </c>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="33"/>
+      <c r="AB25" s="33"/>
+      <c r="AC25" s="33"/>
       <c r="AD25" s="15"/>
-      <c r="AE25" s="13" t="s">
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="33"/>
+      <c r="AH25" s="33"/>
+      <c r="AI25" s="33"/>
+      <c r="AJ25" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK25" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AF25" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG25" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH25" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ25" s="14"/>
-      <c r="AK25" s="15"/>
     </row>
     <row r="26" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G26" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="H26" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="E26" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
       <c r="I26" s="15"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
+      <c r="J26" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="O26" s="33" t="s">
+        <v>46</v>
+      </c>
       <c r="P26" s="15"/>
-      <c r="Q26" s="13"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
+      <c r="Q26" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R26" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="S26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="T26" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="U26" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="V26" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="W26" s="15"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="14"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA26" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB26" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC26" s="33" t="s">
+        <v>129</v>
+      </c>
       <c r="AD26" s="15"/>
-      <c r="AE26" s="13"/>
-      <c r="AF26" s="14"/>
-      <c r="AG26" s="14"/>
-      <c r="AH26" s="14"/>
-      <c r="AI26" s="14"/>
-      <c r="AJ26" s="14"/>
+      <c r="AE26" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF26" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG26" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH26" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI26" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ26" s="33"/>
       <c r="AK26" s="15"/>
     </row>
     <row r="27" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="J27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K27" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="N27" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="O27" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="P27" s="15" t="s">
-        <v>131</v>
-      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="15"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="14"/>
       <c r="S27" s="14"/>
@@ -5801,24 +5817,18 @@
       <c r="V27" s="14"/>
       <c r="W27" s="15"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-      <c r="AB27" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC27" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD27" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="15"/>
       <c r="AE27" s="13"/>
-      <c r="AF27" s="14"/>
-      <c r="AG27" s="14"/>
-      <c r="AH27" s="14"/>
-      <c r="AI27" s="14"/>
-      <c r="AJ27" s="14"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="33"/>
+      <c r="AI27" s="33"/>
+      <c r="AJ27" s="33"/>
       <c r="AK27" s="15"/>
     </row>
     <row r="28" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5826,21 +5836,35 @@
         <v>88</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
       <c r="I28" s="15"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
-      <c r="O28" s="14"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="O28" s="33" t="s">
+        <v>43</v>
+      </c>
       <c r="P28" s="15"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="14"/>
@@ -5849,107 +5873,83 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="15"/>
-      <c r="X28" s="13"/>
-      <c r="Y28" s="14"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="15"/>
-      <c r="AE28" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF28" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG28" s="14"/>
-      <c r="AH28" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI28" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ28" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="X28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y28" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z28" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA28" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD28" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="33"/>
+      <c r="AH28" s="33"/>
+      <c r="AI28" s="33"/>
+      <c r="AJ28" s="33"/>
       <c r="AK28" s="15"/>
     </row>
     <row r="29" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
+        <v>24</v>
+      </c>
+      <c r="C29" s="13"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
       <c r="I29" s="15"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="N29" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O29" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
       <c r="S29" s="14"/>
-      <c r="T29" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="U29" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="V29" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
       <c r="W29" s="15"/>
       <c r="X29" s="13"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB29" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC29" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
+      <c r="AA29" s="33"/>
+      <c r="AB29" s="33"/>
+      <c r="AC29" s="33"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AF29" s="14"/>
-      <c r="AG29" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH29" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI29" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ29" s="14" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="AF29" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AG29" s="33"/>
+      <c r="AH29" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI29" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ29" s="33" t="s">
+        <v>51</v>
       </c>
       <c r="AK29" s="15"/>
     </row>
@@ -5958,348 +5958,340 @@
         <v>89</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
       <c r="I30" s="15"/>
       <c r="J30" s="13"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="P30" s="15"/>
-      <c r="Q30" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="Q30" s="13"/>
       <c r="R30" s="14"/>
-      <c r="S30" s="14"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-      <c r="V30" s="14"/>
+      <c r="S30" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="T30" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="U30" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="V30" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="W30" s="15"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="14"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
+      <c r="Y30" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z30" s="33"/>
+      <c r="AA30" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB30" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC30" s="33" t="s">
+        <v>127</v>
+      </c>
       <c r="AD30" s="15"/>
-      <c r="AE30" s="13"/>
-      <c r="AF30" s="14"/>
-      <c r="AG30" s="14"/>
-      <c r="AH30" s="14"/>
-      <c r="AI30" s="14"/>
-      <c r="AJ30" s="14"/>
+      <c r="AE30" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF30" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG30" s="33"/>
+      <c r="AH30" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI30" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ30" s="33" t="s">
+        <v>50</v>
+      </c>
       <c r="AK30" s="15"/>
     </row>
     <row r="31" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H31" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="13"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="J31" s="13"/>
-      <c r="K31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="M31" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="13"/>
       <c r="R31" s="14"/>
       <c r="S31" s="14"/>
-      <c r="T31" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="U31" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="V31" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="W31" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="X31" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y31" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB31" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC31" s="14" t="s">
-        <v>142</v>
-      </c>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
+      <c r="AA31" s="33"/>
+      <c r="AB31" s="33"/>
+      <c r="AC31" s="33"/>
       <c r="AD31" s="15"/>
       <c r="AE31" s="13"/>
-      <c r="AF31" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG31" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AH31" s="14"/>
-      <c r="AI31" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="AJ31" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AK31" s="15" t="s">
-        <v>44</v>
-      </c>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="33"/>
+      <c r="AH31" s="33"/>
+      <c r="AI31" s="33"/>
+      <c r="AJ31" s="33"/>
+      <c r="AK31" s="15"/>
     </row>
     <row r="32" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I32" s="15" t="s">
-        <v>131</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G32" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" s="15"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14" t="s">
+      <c r="K32" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="M32" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="N32" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="N32" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="O32" s="14" t="s">
-        <v>38</v>
+      <c r="O32" s="33" t="s">
+        <v>140</v>
       </c>
       <c r="P32" s="15"/>
-      <c r="Q32" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R32" s="14" t="s">
-        <v>131</v>
-      </c>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="14"/>
       <c r="S32" s="14" t="s">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U32" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="V32" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="V32" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="W32" s="14"/>
+      <c r="W32" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="X32" s="13"/>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-      <c r="AC32" s="14" t="s">
-        <v>142</v>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC32" s="33" t="s">
+        <v>44</v>
       </c>
       <c r="AD32" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE32" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="AF32" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="AG32" s="14"/>
-      <c r="AH32" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AI32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE32" s="13"/>
+      <c r="AF32" s="33"/>
+      <c r="AG32" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH32" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="AJ32" s="14"/>
-      <c r="AK32" s="15"/>
+      <c r="AI32" s="33"/>
+      <c r="AJ32" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK32" s="15" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="33" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="13"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="G33" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I33" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="13"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="33"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="O33" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="R33" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="S33" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="U33" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
+      <c r="V33" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="W33" s="14"/>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
+      <c r="X33" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y33" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z33" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA33" s="33"/>
+      <c r="AB33" s="33"/>
+      <c r="AC33" s="33"/>
       <c r="AD33" s="15"/>
-      <c r="AE33" s="13"/>
-      <c r="AF33" s="14"/>
-      <c r="AG33" s="14"/>
-      <c r="AH33" s="14"/>
-      <c r="AI33" s="14"/>
-      <c r="AJ33" s="14"/>
+      <c r="AE33" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF33" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG33" s="33"/>
+      <c r="AH33" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI33" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ33" s="33" t="s">
+        <v>139</v>
+      </c>
       <c r="AK33" s="15"/>
     </row>
     <row r="34" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>36</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
       <c r="I34" s="15"/>
       <c r="J34" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K34" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="L34" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="M34" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
+        <v>50</v>
+      </c>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
       <c r="P34" s="15"/>
-      <c r="Q34" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="R34" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="S34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="T34" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U34" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="V34" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="W34" s="15"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
       <c r="X34" s="13"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC34" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
       <c r="AD34" s="15"/>
-      <c r="AE34" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF34" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG34" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH34" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI34" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ34" s="14" t="s">
-        <v>129</v>
-      </c>
+      <c r="AE34" s="13"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="33"/>
+      <c r="AJ34" s="33"/>
       <c r="AK34" s="15"/>
     </row>
     <row r="35" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6307,43 +6299,37 @@
         <v>91</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="14" t="s">
+      <c r="D35" s="33" t="s">
         <v>36</v>
       </c>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="33"/>
       <c r="I35" s="15"/>
       <c r="J35" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="M35" s="14" t="s">
+      <c r="K35" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="N35" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="O35" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="L35" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="13" t="s">
         <v>46</v>
@@ -6352,42 +6338,46 @@
         <v>46</v>
       </c>
       <c r="S35" s="14" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="U35" s="14" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="V35" s="14" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="W35" s="15"/>
-      <c r="X35" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y35" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z35" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA35" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="14"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC35" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="AD35" s="15"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="14"/>
-      <c r="AG35" s="14"/>
-      <c r="AH35" s="14"/>
-      <c r="AI35" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ35" s="14" t="s">
-        <v>129</v>
+      <c r="AE35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF35" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG35" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH35" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI35" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ35" s="33" t="s">
+        <v>127</v>
       </c>
       <c r="AK35" s="15"/>
     </row>
@@ -6396,58 +6386,88 @@
         <v>91</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
+        <v>29</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>141</v>
+      </c>
       <c r="I36" s="15"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14" t="s">
+      <c r="J36" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K36" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="L36" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="O36" s="14" t="s">
+      <c r="O36" s="33" t="s">
         <v>48</v>
       </c>
       <c r="P36" s="15"/>
-      <c r="Q36" s="13"/>
-      <c r="R36" s="14"/>
-      <c r="S36" s="14"/>
-      <c r="T36" s="14"/>
-      <c r="U36" s="14"/>
-      <c r="V36" s="14"/>
+      <c r="Q36" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="R36" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="S36" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="T36" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="U36" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V36" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="W36" s="15"/>
       <c r="X36" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="Y36" s="14" t="s">
+      <c r="Y36" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="Z36" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA36" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="AB36" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC36" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="Z36" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA36" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB36" s="33"/>
+      <c r="AC36" s="33"/>
       <c r="AD36" s="15"/>
       <c r="AE36" s="13"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
-      <c r="AH36" s="14"/>
-      <c r="AI36" s="14"/>
-      <c r="AJ36" s="14"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="33"/>
+      <c r="AH36" s="33"/>
+      <c r="AI36" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ36" s="33" t="s">
+        <v>127</v>
+      </c>
       <c r="AK36" s="15"/>
     </row>
     <row r="37" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6455,19 +6475,25 @@
         <v>91</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+        <v>121</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
       <c r="I37" s="15"/>
       <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
+      <c r="K37" s="33"/>
+      <c r="L37" s="33"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="O37" s="33" t="s">
+        <v>48</v>
+      </c>
       <c r="P37" s="15"/>
       <c r="Q37" s="13"/>
       <c r="R37" s="14"/>
@@ -6476,55 +6502,53 @@
       <c r="U37" s="14"/>
       <c r="V37" s="14"/>
       <c r="W37" s="15"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
+      <c r="X37" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y37" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z37" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA37" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB37" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC37" s="33" t="s">
+        <v>51</v>
+      </c>
       <c r="AD37" s="15"/>
-      <c r="AE37" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF37" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG37" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH37" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="AE37" s="13"/>
+      <c r="AF37" s="33"/>
+      <c r="AG37" s="33"/>
+      <c r="AH37" s="33"/>
+      <c r="AI37" s="33"/>
+      <c r="AJ37" s="33"/>
       <c r="AK37" s="15"/>
     </row>
     <row r="38" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
+        <v>142</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
       <c r="I38" s="15"/>
-      <c r="J38" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
+      <c r="M38" s="33"/>
+      <c r="N38" s="34"/>
+      <c r="O38" s="34"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="14"/>
@@ -6533,31 +6557,27 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
       <c r="W38" s="15"/>
-      <c r="X38" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y38" s="14" t="s">
+      <c r="X38" s="13"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
+      <c r="AC38" s="33"/>
+      <c r="AD38" s="15"/>
+      <c r="AE38" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF38" s="33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG38" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="Z38" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA38" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB38" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC38" s="14"/>
-      <c r="AD38" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="14"/>
-      <c r="AG38" s="14"/>
-      <c r="AH38" s="14"/>
-      <c r="AI38" s="14"/>
-      <c r="AJ38" s="14"/>
+      <c r="AH38" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI38" s="35"/>
+      <c r="AJ38" s="35"/>
       <c r="AK38" s="15"/>
     </row>
     <row r="39" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6565,30 +6585,30 @@
         <v>92</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
+        <v>30</v>
+      </c>
+      <c r="C39" s="13"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
       <c r="I39" s="15"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14" t="s">
+      <c r="J39" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="N39" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="P39" s="15" t="s">
-        <v>46</v>
-      </c>
+      <c r="K39" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M39" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="15"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="14"/>
       <c r="S39" s="14"/>
@@ -6597,30 +6617,30 @@
       <c r="V39" s="14"/>
       <c r="W39" s="15"/>
       <c r="X39" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y39" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z39" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA39" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33" t="s">
         <v>36</v>
-      </c>
-      <c r="Y39" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z39" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA39" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="14" t="s">
-        <v>50</v>
       </c>
       <c r="AD39" s="15" t="s">
         <v>44</v>
       </c>
       <c r="AE39" s="13"/>
-      <c r="AF39" s="14"/>
-      <c r="AG39" s="14"/>
-      <c r="AH39" s="14"/>
-      <c r="AI39" s="14"/>
-      <c r="AJ39" s="14"/>
+      <c r="AF39" s="33"/>
+      <c r="AG39" s="33"/>
+      <c r="AH39" s="33"/>
+      <c r="AI39" s="33"/>
+      <c r="AJ39" s="33"/>
       <c r="AK39" s="15"/>
     </row>
     <row r="40" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6628,33 +6648,33 @@
         <v>92</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
       <c r="I40" s="15"/>
       <c r="J40" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="L40" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="M40" s="33"/>
+      <c r="N40" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="O40" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="P40" s="15" t="s">
         <v>38</v>
-      </c>
-      <c r="O40" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>46</v>
       </c>
       <c r="Q40" s="13"/>
       <c r="R40" s="14"/>
@@ -6664,150 +6684,160 @@
       <c r="V40" s="14"/>
       <c r="W40" s="15"/>
       <c r="X40" s="13"/>
-      <c r="Y40" s="14"/>
-      <c r="Z40" s="14"/>
-      <c r="AA40" s="14"/>
-      <c r="AB40" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC40" s="14" t="s">
+      <c r="Y40" s="33"/>
+      <c r="Z40" s="33"/>
+      <c r="AA40" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB40" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="AD40" s="15"/>
+      <c r="AC40" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD40" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="AE40" s="13"/>
-      <c r="AF40" s="14"/>
-      <c r="AG40" s="14"/>
-      <c r="AH40" s="14"/>
-      <c r="AI40" s="14"/>
-      <c r="AJ40" s="14"/>
+      <c r="AF40" s="33"/>
+      <c r="AG40" s="33"/>
+      <c r="AH40" s="33"/>
+      <c r="AI40" s="33"/>
+      <c r="AJ40" s="33"/>
       <c r="AK40" s="15"/>
     </row>
     <row r="41" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
+        <v>49</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
       <c r="I41" s="15"/>
       <c r="J41" s="13"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="15"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
+      <c r="M41" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="O41" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="P41" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="Q41" s="13"/>
-      <c r="R41" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="S41" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="R41" s="14"/>
+      <c r="S41" s="14"/>
       <c r="T41" s="14"/>
       <c r="U41" s="14"/>
-      <c r="V41" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="W41" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="14"/>
-      <c r="Z41" s="14"/>
-      <c r="AA41" s="14"/>
-      <c r="AB41" s="14"/>
-      <c r="AC41" s="14"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="15"/>
+      <c r="X41" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y41" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z41" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA41" s="33"/>
+      <c r="AB41" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC41" s="33"/>
       <c r="AD41" s="15"/>
       <c r="AE41" s="13"/>
-      <c r="AF41" s="14"/>
-      <c r="AG41" s="14" t="s">
+      <c r="AF41" s="33"/>
+      <c r="AG41" s="33"/>
+      <c r="AH41" s="33"/>
+      <c r="AI41" s="33"/>
+      <c r="AJ41" s="33"/>
+      <c r="AK41" s="15"/>
+    </row>
+    <row r="42" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AH41" s="14"/>
-      <c r="AI41" s="14"/>
-      <c r="AJ41" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK41" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
+      <c r="I42" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="J42" s="13"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
       <c r="P42" s="15"/>
       <c r="Q42" s="13"/>
-      <c r="R42" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S42" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="R42" s="14"/>
+      <c r="S42" s="14"/>
       <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
+      <c r="U42" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="V42" s="14" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="W42" s="15" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="X42" s="13"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
-      <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
-      <c r="AC42" s="14"/>
+      <c r="Y42" s="33"/>
+      <c r="Z42" s="33"/>
+      <c r="AA42" s="33"/>
+      <c r="AB42" s="33"/>
+      <c r="AC42" s="33"/>
       <c r="AD42" s="15"/>
       <c r="AE42" s="13"/>
-      <c r="AF42" s="14"/>
-      <c r="AG42" s="14"/>
-      <c r="AH42" s="14"/>
-      <c r="AI42" s="14"/>
-      <c r="AJ42" s="14" t="s">
-        <v>36</v>
+      <c r="AF42" s="33"/>
+      <c r="AG42" s="33"/>
+      <c r="AH42" s="33"/>
+      <c r="AI42" s="33"/>
+      <c r="AJ42" s="33" t="s">
+        <v>47</v>
       </c>
       <c r="AK42" s="15" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="C43" s="16"/>
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="17"/>
       <c r="H43" s="17"/>
-      <c r="I43" s="18"/>
+      <c r="I43" s="18" t="s">
+        <v>51</v>
+      </c>
       <c r="J43" s="16"/>
       <c r="K43" s="17"/>
       <c r="L43" s="17"/>
@@ -6819,9 +6849,15 @@
       <c r="R43" s="17"/>
       <c r="S43" s="17"/>
       <c r="T43" s="17"/>
-      <c r="U43" s="17"/>
-      <c r="V43" s="17"/>
-      <c r="W43" s="18"/>
+      <c r="U43" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="V43" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W43" s="18" t="s">
+        <v>129</v>
+      </c>
       <c r="X43" s="16"/>
       <c r="Y43" s="17"/>
       <c r="Z43" s="17"/>
@@ -6831,16 +6867,14 @@
       <c r="AD43" s="18"/>
       <c r="AE43" s="16"/>
       <c r="AF43" s="17"/>
-      <c r="AG43" s="17" t="s">
-        <v>37</v>
-      </c>
+      <c r="AG43" s="17"/>
       <c r="AH43" s="17"/>
       <c r="AI43" s="17"/>
       <c r="AJ43" s="17" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="AK43" s="18" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -6853,4 +6887,40 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52035135-8425-4836-86D4-4F41DD6F73C0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C041FD6-E0E7-43A0-B74A-FBD0BB01C881}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03CCA481-E940-4958-95E3-F3125561ED2E}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FA72D37-6E1E-44EE-B1EF-84C46CC2AA50}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Raspored.xlsx
+++ b/Raspored.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raspored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F8F702-B9DC-40A1-8405-511504A416D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD30EE25-31F4-4E64-8BB4-0150AADF1BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E29FE33D-0FD8-4EFA-99F6-035E72B381D0}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="161">
   <si>
     <t>ПОНЕДЕЉАК</t>
   </si>
@@ -752,7 +752,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -848,15 +848,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1393,7 +1384,9 @@
       <c r="K3" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="M3" s="11" t="s">
         <v>98</v>
       </c>
@@ -1556,7 +1549,9 @@
       <c r="J5" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="K5" s="14"/>
+      <c r="K5" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="L5" s="14" t="s">
         <v>102</v>
       </c>
@@ -1876,7 +1871,9 @@
       <c r="S10" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="T10" s="14"/>
+      <c r="T10" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="U10" s="14" t="s">
         <v>107</v>
       </c>
@@ -1945,7 +1942,9 @@
       <c r="S11" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="T11" s="14"/>
+      <c r="T11" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="U11" s="14" t="s">
         <v>73</v>
       </c>
@@ -2008,7 +2007,9 @@
       <c r="S12" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="T12" s="14"/>
+      <c r="T12" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="U12" s="14" t="s">
         <v>73</v>
       </c>
@@ -2139,7 +2140,9 @@
       <c r="X14" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="Y14" s="14"/>
+      <c r="Y14" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="Z14" s="14" t="s">
         <v>102</v>
       </c>
@@ -2342,7 +2345,9 @@
       <c r="L17" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="M17" s="14"/>
+      <c r="M17" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="N17" s="14" t="s">
         <v>73</v>
       </c>
@@ -2492,7 +2497,9 @@
       <c r="Z19" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="AA19" s="14"/>
+      <c r="AA19" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AB19" s="14" t="s">
         <v>71</v>
       </c>
@@ -2621,7 +2628,9 @@
       <c r="AA21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AB21" s="14"/>
+      <c r="AB21" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AC21" s="14" t="s">
         <v>74</v>
       </c>
@@ -2914,7 +2923,9 @@
       <c r="K26" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="L26" s="14"/>
+      <c r="L26" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="M26" s="14" t="s">
         <v>76</v>
       </c>
@@ -3125,7 +3136,9 @@
       <c r="AA29" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="AB29" s="14"/>
+      <c r="AB29" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AC29" s="14" t="s">
         <v>34</v>
       </c>
@@ -3161,7 +3174,9 @@
       <c r="L30" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="M30" s="14"/>
+      <c r="M30" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="N30" s="14" t="s">
         <v>75</v>
       </c>
@@ -3370,7 +3385,9 @@
       <c r="AG32" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="AH32" s="14"/>
+      <c r="AH32" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AI32" s="14" t="s">
         <v>102</v>
       </c>
@@ -3406,7 +3423,9 @@
       <c r="L33" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="M33" s="14"/>
+      <c r="M33" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="N33" s="14" t="s">
         <v>76</v>
       </c>
@@ -3497,7 +3516,9 @@
       <c r="L34" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="M34" s="14"/>
+      <c r="M34" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="N34" s="14" t="s">
         <v>76</v>
       </c>
@@ -4206,7 +4227,9 @@
       <c r="AG3" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="AH3" s="11"/>
+      <c r="AH3" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AI3" s="11" t="s">
         <v>45</v>
       </c>
@@ -4223,32 +4246,32 @@
         <v>6</v>
       </c>
       <c r="C4" s="13"/>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="33" t="s">
+      <c r="H4" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I4" s="15"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33" t="s">
+      <c r="K4" s="14"/>
+      <c r="L4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="M4" s="33" t="s">
+      <c r="M4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="33" t="s">
+      <c r="N4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="O4" s="33" t="s">
+      <c r="O4" s="14" t="s">
         <v>50</v>
       </c>
       <c r="P4" s="15"/>
@@ -4270,32 +4293,32 @@
       <c r="X4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="Y4" s="33" t="s">
+      <c r="Y4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="Z4" s="33" t="s">
+      <c r="Z4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="33" t="s">
+      <c r="AA4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="14"/>
       <c r="AD4" s="15"/>
       <c r="AE4" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AF4" s="33" t="s">
+      <c r="AF4" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AG4" s="33" t="s">
+      <c r="AG4" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AH4" s="33"/>
-      <c r="AI4" s="33" t="s">
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AJ4" s="33" t="s">
+      <c r="AJ4" s="14" t="s">
         <v>46</v>
       </c>
       <c r="AK4" s="15"/>
@@ -4310,24 +4333,24 @@
       <c r="C5" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
       <c r="I5" s="15"/>
       <c r="J5" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="13" t="s">
         <v>43</v>
@@ -4336,29 +4359,31 @@
         <v>37</v>
       </c>
       <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
+      <c r="T5" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
       <c r="W5" s="15"/>
       <c r="X5" s="13"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33" t="s">
+      <c r="Y5" s="14"/>
+      <c r="Z5" s="14"/>
+      <c r="AA5" s="14"/>
+      <c r="AB5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AC5" s="33" t="s">
+      <c r="AC5" s="14" t="s">
         <v>37</v>
       </c>
       <c r="AD5" s="15"/>
       <c r="AE5" s="13"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="33" t="s">
+      <c r="AF5" s="14"/>
+      <c r="AG5" s="14"/>
+      <c r="AH5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="33"/>
+      <c r="AI5" s="14"/>
+      <c r="AJ5" s="14"/>
       <c r="AK5" s="15"/>
     </row>
     <row r="6" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4369,30 +4394,30 @@
         <v>54</v>
       </c>
       <c r="C6" s="13"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="33" t="s">
+      <c r="G6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="33" t="s">
+      <c r="K6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="33" t="s">
+      <c r="L6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="33"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
       <c r="P6" s="15"/>
       <c r="Q6" s="13" t="s">
         <v>35</v>
@@ -4408,26 +4433,28 @@
       <c r="V6" s="14"/>
       <c r="W6" s="15"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33" t="s">
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="14"/>
+      <c r="AB6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AC6" s="33" t="s">
+      <c r="AC6" s="14" t="s">
         <v>130</v>
       </c>
       <c r="AD6" s="15"/>
       <c r="AE6" s="13"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33" t="s">
+      <c r="AF6" s="14"/>
+      <c r="AG6" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AH6" s="33"/>
-      <c r="AI6" s="33" t="s">
+      <c r="AH6" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI6" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AJ6" s="33" t="s">
+      <c r="AJ6" s="14" t="s">
         <v>129</v>
       </c>
       <c r="AK6" s="15"/>
@@ -4440,18 +4467,18 @@
         <v>54</v>
       </c>
       <c r="C7" s="13"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
       <c r="I7" s="15"/>
       <c r="J7" s="13"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
       <c r="P7" s="15"/>
       <c r="Q7" s="13"/>
       <c r="R7" s="14"/>
@@ -4461,18 +4488,18 @@
       <c r="V7" s="14"/>
       <c r="W7" s="15"/>
       <c r="X7" s="13"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="14"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
       <c r="AD7" s="15"/>
       <c r="AE7" s="13"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="33"/>
-      <c r="AH7" s="33"/>
-      <c r="AI7" s="33"/>
-      <c r="AJ7" s="33"/>
+      <c r="AF7" s="14"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+      <c r="AJ7" s="14"/>
       <c r="AK7" s="15" t="s">
         <v>131</v>
       </c>
@@ -4485,30 +4512,32 @@
         <v>8</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="33" t="s">
+      <c r="H8" s="14" t="s">
         <v>46</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="33" t="s">
+      <c r="K8" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33" t="s">
+      <c r="L8" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="N8" s="33" t="s">
+      <c r="N8" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="33" t="s">
+      <c r="O8" s="14" t="s">
         <v>38</v>
       </c>
       <c r="P8" s="15"/>
@@ -4526,34 +4555,34 @@
       <c r="X8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="Y8" s="33" t="s">
+      <c r="Y8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="33" t="s">
+      <c r="Z8" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AA8" s="33" t="s">
+      <c r="AA8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AB8" s="33" t="s">
+      <c r="AB8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AC8" s="33" t="s">
+      <c r="AC8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="AD8" s="15"/>
       <c r="AE8" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AF8" s="33" t="s">
+      <c r="AF8" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AG8" s="33" t="s">
+      <c r="AG8" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="33"/>
+      <c r="AH8" s="14"/>
+      <c r="AI8" s="14"/>
+      <c r="AJ8" s="14"/>
       <c r="AK8" s="15"/>
     </row>
     <row r="9" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4566,24 +4595,24 @@
       <c r="C9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
       <c r="I9" s="15"/>
       <c r="J9" s="13"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
       <c r="P9" s="15"/>
       <c r="Q9" s="13"/>
       <c r="R9" s="14"/>
@@ -4601,22 +4630,22 @@
       </c>
       <c r="W9" s="15"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
+      <c r="Y9" s="14"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="14"/>
+      <c r="AB9" s="14"/>
+      <c r="AC9" s="14"/>
       <c r="AD9" s="15"/>
       <c r="AE9" s="13"/>
-      <c r="AF9" s="33"/>
-      <c r="AG9" s="33"/>
-      <c r="AH9" s="33" t="s">
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="14"/>
+      <c r="AH9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AI9" s="33" t="s">
+      <c r="AI9" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="AJ9" s="33" t="s">
+      <c r="AJ9" s="14" t="s">
         <v>44</v>
       </c>
       <c r="AK9" s="15"/>
@@ -4629,24 +4658,24 @@
         <v>10</v>
       </c>
       <c r="C10" s="13"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
       <c r="I10" s="15"/>
       <c r="J10" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="K10" s="33"/>
-      <c r="L10" s="33" t="s">
+      <c r="K10" s="14"/>
+      <c r="L10" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="M10" s="33" t="s">
+      <c r="M10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="N10" s="33"/>
-      <c r="O10" s="33"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
       <c r="P10" s="15"/>
       <c r="Q10" s="13"/>
       <c r="R10" s="14"/>
@@ -4656,24 +4685,24 @@
       <c r="V10" s="14"/>
       <c r="W10" s="15"/>
       <c r="X10" s="13"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33" t="s">
+      <c r="Y10" s="14"/>
+      <c r="Z10" s="14"/>
+      <c r="AA10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AB10" s="33" t="s">
+      <c r="AB10" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="AC10" s="33" t="s">
+      <c r="AC10" s="14" t="s">
         <v>131</v>
       </c>
       <c r="AD10" s="15"/>
       <c r="AE10" s="13"/>
-      <c r="AF10" s="33"/>
-      <c r="AG10" s="33"/>
-      <c r="AH10" s="33"/>
-      <c r="AI10" s="33"/>
-      <c r="AJ10" s="33"/>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="14"/>
+      <c r="AH10" s="14"/>
+      <c r="AI10" s="14"/>
+      <c r="AJ10" s="14"/>
       <c r="AK10" s="15"/>
     </row>
     <row r="11" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4684,24 +4713,24 @@
         <v>11</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
       <c r="I11" s="15"/>
       <c r="J11" s="13"/>
-      <c r="K11" s="33" t="s">
+      <c r="K11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33" t="s">
+      <c r="L11" s="14"/>
+      <c r="M11" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="N11" s="33" t="s">
+      <c r="N11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="33" t="s">
+      <c r="O11" s="14" t="s">
         <v>36</v>
       </c>
       <c r="P11" s="15"/>
@@ -4715,24 +4744,24 @@
       <c r="X11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="Y11" s="33" t="s">
+      <c r="Y11" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Z11" s="33" t="s">
+      <c r="Z11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AA11" s="33" t="s">
+      <c r="AA11" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="14"/>
       <c r="AD11" s="15"/>
       <c r="AE11" s="13"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="33"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="14"/>
+      <c r="AH11" s="14"/>
+      <c r="AI11" s="14"/>
+      <c r="AJ11" s="14"/>
       <c r="AK11" s="15"/>
     </row>
     <row r="12" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4743,22 +4772,22 @@
         <v>12</v>
       </c>
       <c r="C12" s="13"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
       <c r="I12" s="15"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="33"/>
-      <c r="M12" s="33" t="s">
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="N12" s="33" t="s">
+      <c r="N12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="O12" s="33" t="s">
+      <c r="O12" s="14" t="s">
         <v>135</v>
       </c>
       <c r="P12" s="15"/>
@@ -4772,22 +4801,24 @@
       <c r="X12" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33" t="s">
+      <c r="Y12" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="Z12" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="AA12" s="33" t="s">
+      <c r="AA12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
+      <c r="AB12" s="14"/>
+      <c r="AC12" s="14"/>
       <c r="AD12" s="15"/>
       <c r="AE12" s="13"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="33"/>
-      <c r="AH12" s="33"/>
-      <c r="AI12" s="33"/>
-      <c r="AJ12" s="33"/>
+      <c r="AF12" s="14"/>
+      <c r="AG12" s="14"/>
+      <c r="AH12" s="14"/>
+      <c r="AI12" s="14"/>
+      <c r="AJ12" s="14"/>
       <c r="AK12" s="15"/>
     </row>
     <row r="13" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4798,22 +4829,22 @@
         <v>13</v>
       </c>
       <c r="C13" s="13"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
       <c r="I13" s="15"/>
       <c r="J13" s="13"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="33" t="s">
+      <c r="K13" s="14"/>
+      <c r="L13" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="M13" s="33" t="s">
+      <c r="M13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33" t="s">
+      <c r="N13" s="14"/>
+      <c r="O13" s="14" t="s">
         <v>69</v>
       </c>
       <c r="P13" s="15"/>
@@ -4825,24 +4856,24 @@
       <c r="V13" s="14"/>
       <c r="W13" s="15"/>
       <c r="X13" s="13"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33" t="s">
+      <c r="Y13" s="14"/>
+      <c r="Z13" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AA13" s="33" t="s">
+      <c r="AA13" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="AB13" s="33" t="s">
+      <c r="AB13" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="AC13" s="33"/>
+      <c r="AC13" s="14"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="13"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="33"/>
-      <c r="AH13" s="33"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="33"/>
+      <c r="AF13" s="14"/>
+      <c r="AG13" s="14"/>
+      <c r="AH13" s="14"/>
+      <c r="AI13" s="14"/>
+      <c r="AJ13" s="14"/>
       <c r="AK13" s="15"/>
     </row>
     <row r="14" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4853,26 +4884,28 @@
         <v>39</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
       <c r="I14" s="15"/>
       <c r="J14" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33" t="s">
+      <c r="L14" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="N14" s="33" t="s">
+      <c r="N14" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="O14" s="33" t="s">
+      <c r="O14" s="14" t="s">
         <v>47</v>
       </c>
       <c r="P14" s="15"/>
@@ -4886,28 +4919,28 @@
       <c r="X14" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="Y14" s="33" t="s">
+      <c r="Y14" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="Z14" s="33" t="s">
+      <c r="Z14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AA14" s="33" t="s">
+      <c r="AA14" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AB14" s="33" t="s">
+      <c r="AB14" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="AC14" s="33" t="s">
+      <c r="AC14" s="14" t="s">
         <v>131</v>
       </c>
       <c r="AD14" s="15"/>
       <c r="AE14" s="13"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="33"/>
-      <c r="AH14" s="33"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="33"/>
+      <c r="AF14" s="14"/>
+      <c r="AG14" s="14"/>
+      <c r="AH14" s="14"/>
+      <c r="AI14" s="14"/>
+      <c r="AJ14" s="14"/>
       <c r="AK14" s="15"/>
     </row>
     <row r="15" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -4920,32 +4953,34 @@
       <c r="C15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33" t="s">
+      <c r="D15" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="F15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
       <c r="I15" s="15"/>
       <c r="J15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="33" t="s">
+      <c r="K15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L15" s="33" t="s">
+      <c r="L15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="M15" s="33" t="s">
+      <c r="M15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="N15" s="33" t="s">
+      <c r="N15" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="33"/>
+      <c r="O15" s="14"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="13" t="s">
         <v>48</v>
@@ -4967,30 +5002,30 @@
       <c r="X15" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="Y15" s="33" t="s">
+      <c r="Y15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="Z15" s="33" t="s">
+      <c r="Z15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="14"/>
       <c r="AD15" s="15"/>
       <c r="AE15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="33" t="s">
+      <c r="AF15" s="14"/>
+      <c r="AG15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AH15" s="33" t="s">
+      <c r="AH15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AI15" s="33" t="s">
+      <c r="AI15" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AJ15" s="33" t="s">
+      <c r="AJ15" s="14" t="s">
         <v>95</v>
       </c>
       <c r="AK15" s="15"/>
@@ -5005,34 +5040,34 @@
       <c r="C16" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33" t="s">
+      <c r="F16" s="14"/>
+      <c r="G16" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="14" t="s">
         <v>137</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="K16" s="33" t="s">
+      <c r="K16" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="L16" s="33" t="s">
+      <c r="L16" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="M16" s="33" t="s">
+      <c r="M16" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="14"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="13" t="s">
         <v>37</v>
@@ -5054,30 +5089,30 @@
       <c r="X16" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="Y16" s="33" t="s">
+      <c r="Y16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33" t="s">
+      <c r="Z16" s="14"/>
+      <c r="AA16" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
+      <c r="AB16" s="14"/>
+      <c r="AC16" s="14"/>
       <c r="AD16" s="15"/>
       <c r="AE16" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AF16" s="33" t="s">
+      <c r="AF16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AG16" s="33" t="s">
+      <c r="AG16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AH16" s="33" t="s">
+      <c r="AH16" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AI16" s="33"/>
-      <c r="AJ16" s="33"/>
+      <c r="AI16" s="14"/>
+      <c r="AJ16" s="14"/>
       <c r="AK16" s="15"/>
     </row>
     <row r="17" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5088,22 +5123,22 @@
         <v>16</v>
       </c>
       <c r="C17" s="13"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="33"/>
+      <c r="H17" s="14"/>
       <c r="I17" s="15"/>
       <c r="J17" s="13"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="13" t="s">
         <v>50</v>
@@ -5121,22 +5156,24 @@
       <c r="V17" s="14"/>
       <c r="W17" s="15"/>
       <c r="X17" s="13"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
       <c r="AD17" s="15"/>
       <c r="AE17" s="13"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="33" t="s">
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AH17" s="33"/>
-      <c r="AI17" s="33" t="s">
+      <c r="AH17" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI17" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AJ17" s="33"/>
+      <c r="AJ17" s="14"/>
       <c r="AK17" s="15"/>
     </row>
     <row r="18" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5149,22 +5186,22 @@
       <c r="C18" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
       <c r="I18" s="15"/>
       <c r="J18" s="13"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
       <c r="P18" s="15"/>
       <c r="Q18" s="13"/>
       <c r="R18" s="14"/>
@@ -5176,26 +5213,26 @@
       <c r="X18" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="Y18" s="33" t="s">
+      <c r="Y18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="Z18" s="33" t="s">
+      <c r="Z18" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
       <c r="AD18" s="15"/>
       <c r="AE18" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AF18" s="33" t="s">
+      <c r="AF18" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AG18" s="33"/>
-      <c r="AH18" s="33"/>
-      <c r="AI18" s="33"/>
-      <c r="AJ18" s="33"/>
+      <c r="AG18" s="14"/>
+      <c r="AH18" s="14"/>
+      <c r="AI18" s="14"/>
+      <c r="AJ18" s="14"/>
       <c r="AK18" s="15"/>
     </row>
     <row r="19" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5208,32 +5245,32 @@
       <c r="C19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="E19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33" t="s">
+      <c r="F19" s="14"/>
+      <c r="G19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="14" t="s">
         <v>47</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="L19" s="33" t="s">
+      <c r="L19" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
       <c r="P19" s="15"/>
       <c r="Q19" s="13" t="s">
         <v>47</v>
@@ -5257,32 +5294,32 @@
       <c r="X19" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="Y19" s="33" t="s">
+      <c r="Y19" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="Z19" s="33" t="s">
+      <c r="Z19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
       <c r="AD19" s="15"/>
       <c r="AE19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AF19" s="33" t="s">
+      <c r="AF19" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AG19" s="33" t="s">
+      <c r="AG19" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AH19" s="33" t="s">
+      <c r="AH19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AI19" s="33" t="s">
+      <c r="AI19" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AJ19" s="33"/>
+      <c r="AJ19" s="14"/>
       <c r="AK19" s="15"/>
     </row>
     <row r="20" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5295,28 +5332,28 @@
       <c r="C20" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="H20" s="14" t="s">
         <v>38</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="13"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
       <c r="P20" s="15"/>
       <c r="Q20" s="13"/>
       <c r="R20" s="14" t="s">
@@ -5334,26 +5371,26 @@
       </c>
       <c r="W20" s="15"/>
       <c r="X20" s="13"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="33"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
       <c r="AD20" s="15"/>
       <c r="AE20" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AF20" s="33" t="s">
+      <c r="AF20" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AG20" s="33" t="s">
+      <c r="AG20" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AH20" s="33" t="s">
+      <c r="AH20" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AI20" s="33"/>
-      <c r="AJ20" s="33"/>
+      <c r="AI20" s="14"/>
+      <c r="AJ20" s="14"/>
       <c r="AK20" s="15"/>
     </row>
     <row r="21" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5366,32 +5403,32 @@
       <c r="C21" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="15"/>
       <c r="J21" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="K21" s="33" t="s">
+      <c r="K21" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="33" t="s">
+      <c r="L21" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="M21" s="33" t="s">
+      <c r="M21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="N21" s="33" t="s">
+      <c r="N21" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="O21" s="33" t="s">
+      <c r="O21" s="14" t="s">
         <v>35</v>
       </c>
       <c r="P21" s="15"/>
@@ -5411,34 +5448,36 @@
       <c r="X21" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Y21" s="33" t="s">
+      <c r="Y21" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33" t="s">
+      <c r="Z21" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA21" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AB21" s="33" t="s">
+      <c r="AB21" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AC21" s="33" t="s">
+      <c r="AC21" s="14" t="s">
         <v>43</v>
       </c>
       <c r="AD21" s="15"/>
       <c r="AE21" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AF21" s="33" t="s">
+      <c r="AF21" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AG21" s="33" t="s">
+      <c r="AG21" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AH21" s="33" t="s">
+      <c r="AH21" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="33"/>
+      <c r="AI21" s="14"/>
+      <c r="AJ21" s="14"/>
       <c r="AK21" s="15"/>
     </row>
     <row r="22" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5449,24 +5488,24 @@
         <v>20</v>
       </c>
       <c r="C22" s="13"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="14" t="s">
         <v>51</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="13"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
       <c r="P22" s="15"/>
       <c r="Q22" s="13" t="s">
         <v>45</v>
@@ -5482,20 +5521,20 @@
       <c r="V22" s="14"/>
       <c r="W22" s="15"/>
       <c r="X22" s="13"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
       <c r="AD22" s="15"/>
       <c r="AE22" s="13"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="33"/>
-      <c r="AH22" s="33"/>
-      <c r="AI22" s="33" t="s">
+      <c r="AF22" s="14"/>
+      <c r="AG22" s="14"/>
+      <c r="AH22" s="14"/>
+      <c r="AI22" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AJ22" s="33" t="s">
+      <c r="AJ22" s="14" t="s">
         <v>37</v>
       </c>
       <c r="AK22" s="15"/>
@@ -5508,36 +5547,36 @@
         <v>21</v>
       </c>
       <c r="C23" s="13"/>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="14" t="s">
         <v>44</v>
       </c>
       <c r="I23" s="15"/>
       <c r="J23" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="K23" s="33" t="s">
+      <c r="K23" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="33" t="s">
+      <c r="L23" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33" t="s">
+      <c r="M23" s="14"/>
+      <c r="N23" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="O23" s="33" t="s">
+      <c r="O23" s="14" t="s">
         <v>159</v>
       </c>
       <c r="P23" s="15"/>
@@ -5557,32 +5596,32 @@
       <c r="X23" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="Y23" s="33" t="s">
+      <c r="Y23" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Z23" s="33" t="s">
+      <c r="Z23" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33" t="s">
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AC23" s="33" t="s">
+      <c r="AC23" s="14" t="s">
         <v>50</v>
       </c>
       <c r="AD23" s="15"/>
       <c r="AE23" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AF23" s="33" t="s">
+      <c r="AF23" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AG23" s="33" t="s">
+      <c r="AG23" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AH23" s="33"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="33"/>
+      <c r="AH23" s="14"/>
+      <c r="AI23" s="14"/>
+      <c r="AJ23" s="14"/>
       <c r="AK23" s="15"/>
     </row>
     <row r="24" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5593,20 +5632,20 @@
         <v>22</v>
       </c>
       <c r="C24" s="13"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="33"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="15"/>
       <c r="J24" s="13"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="13"/>
       <c r="R24" s="14"/>
@@ -5618,22 +5657,22 @@
       <c r="V24" s="14"/>
       <c r="W24" s="15"/>
       <c r="X24" s="13"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="33"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
       <c r="AD24" s="15"/>
       <c r="AE24" s="13"/>
-      <c r="AF24" s="33"/>
-      <c r="AG24" s="33"/>
-      <c r="AH24" s="33" t="s">
+      <c r="AF24" s="14"/>
+      <c r="AG24" s="14"/>
+      <c r="AH24" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AI24" s="33" t="s">
+      <c r="AI24" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AJ24" s="33"/>
+      <c r="AJ24" s="14"/>
       <c r="AK24" s="15"/>
     </row>
     <row r="25" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5644,22 +5683,22 @@
         <v>22</v>
       </c>
       <c r="C25" s="13"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33" t="s">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>134</v>
       </c>
       <c r="J25" s="13"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="13"/>
       <c r="R25" s="17"/>
@@ -5675,18 +5714,18 @@
         <v>132</v>
       </c>
       <c r="X25" s="13"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="33"/>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
       <c r="AD25" s="15"/>
       <c r="AE25" s="13"/>
-      <c r="AF25" s="33"/>
-      <c r="AG25" s="33"/>
-      <c r="AH25" s="33"/>
-      <c r="AI25" s="33"/>
-      <c r="AJ25" s="33" t="s">
+      <c r="AF25" s="14"/>
+      <c r="AG25" s="14"/>
+      <c r="AH25" s="14"/>
+      <c r="AI25" s="14"/>
+      <c r="AJ25" s="14" t="s">
         <v>144</v>
       </c>
       <c r="AK25" s="15" t="s">
@@ -5703,30 +5742,30 @@
       <c r="C26" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="33"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="15"/>
       <c r="J26" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="33" t="s">
+      <c r="L26" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="33"/>
-      <c r="N26" s="33" t="s">
+      <c r="M26" s="14"/>
+      <c r="N26" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="O26" s="33" t="s">
+      <c r="O26" s="14" t="s">
         <v>46</v>
       </c>
       <c r="P26" s="15"/>
@@ -5750,36 +5789,36 @@
       </c>
       <c r="W26" s="15"/>
       <c r="X26" s="13"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33" t="s">
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AA26" s="33" t="s">
+      <c r="AA26" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AB26" s="33" t="s">
+      <c r="AB26" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AC26" s="33" t="s">
+      <c r="AC26" s="14" t="s">
         <v>129</v>
       </c>
       <c r="AD26" s="15"/>
       <c r="AE26" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AF26" s="33" t="s">
+      <c r="AF26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AG26" s="33" t="s">
+      <c r="AG26" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AH26" s="33" t="s">
+      <c r="AH26" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AI26" s="33" t="s">
+      <c r="AI26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AJ26" s="33"/>
+      <c r="AJ26" s="14"/>
       <c r="AK26" s="15"/>
     </row>
     <row r="27" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5790,24 +5829,24 @@
         <v>62</v>
       </c>
       <c r="C27" s="13"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33" t="s">
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="33" t="s">
+      <c r="H27" s="14" t="s">
         <v>48</v>
       </c>
       <c r="I27" s="15"/>
       <c r="J27" s="13"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
       <c r="P27" s="15"/>
       <c r="Q27" s="13"/>
       <c r="R27" s="14"/>
@@ -5817,18 +5856,18 @@
       <c r="V27" s="14"/>
       <c r="W27" s="15"/>
       <c r="X27" s="13"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="33"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
       <c r="AD27" s="15"/>
       <c r="AE27" s="13"/>
-      <c r="AF27" s="33"/>
-      <c r="AG27" s="33"/>
-      <c r="AH27" s="33"/>
-      <c r="AI27" s="33"/>
-      <c r="AJ27" s="33"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="14"/>
+      <c r="AJ27" s="14"/>
       <c r="AK27" s="15"/>
     </row>
     <row r="28" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5841,28 +5880,28 @@
       <c r="C28" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
       <c r="I28" s="15"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33" t="s">
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="N28" s="33" t="s">
+      <c r="N28" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="O28" s="33" t="s">
+      <c r="O28" s="14" t="s">
         <v>43</v>
       </c>
       <c r="P28" s="15"/>
@@ -5876,28 +5915,30 @@
       <c r="X28" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="Y28" s="33" t="s">
+      <c r="Y28" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="Z28" s="33" t="s">
+      <c r="Z28" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AA28" s="33" t="s">
+      <c r="AA28" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="33" t="s">
+      <c r="AB28" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC28" s="14" t="s">
         <v>38</v>
       </c>
       <c r="AD28" s="15" t="s">
         <v>50</v>
       </c>
       <c r="AE28" s="13"/>
-      <c r="AF28" s="33"/>
-      <c r="AG28" s="33"/>
-      <c r="AH28" s="33"/>
-      <c r="AI28" s="33"/>
-      <c r="AJ28" s="33"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="14"/>
+      <c r="AH28" s="14"/>
+      <c r="AI28" s="14"/>
+      <c r="AJ28" s="14"/>
       <c r="AK28" s="15"/>
     </row>
     <row r="29" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5908,18 +5949,18 @@
         <v>24</v>
       </c>
       <c r="C29" s="13"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
       <c r="I29" s="15"/>
       <c r="J29" s="13"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
       <c r="P29" s="15"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
@@ -5929,26 +5970,26 @@
       <c r="V29" s="14"/>
       <c r="W29" s="15"/>
       <c r="X29" s="13"/>
-      <c r="Y29" s="33"/>
-      <c r="Z29" s="33"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="33"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AF29" s="33" t="s">
+      <c r="AF29" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AG29" s="33"/>
-      <c r="AH29" s="33" t="s">
+      <c r="AG29" s="14"/>
+      <c r="AH29" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AI29" s="33" t="s">
+      <c r="AI29" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AJ29" s="33" t="s">
+      <c r="AJ29" s="14" t="s">
         <v>51</v>
       </c>
       <c r="AK29" s="15"/>
@@ -5963,24 +6004,24 @@
       <c r="C30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
       <c r="I30" s="15"/>
       <c r="J30" s="13"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33" t="s">
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="O30" s="33" t="s">
+      <c r="O30" s="14" t="s">
         <v>51</v>
       </c>
       <c r="P30" s="15"/>
@@ -6000,34 +6041,36 @@
       </c>
       <c r="W30" s="15"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="33" t="s">
+      <c r="Y30" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="Z30" s="33"/>
-      <c r="AA30" s="33" t="s">
+      <c r="Z30" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA30" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="AB30" s="33" t="s">
+      <c r="AB30" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AC30" s="33" t="s">
+      <c r="AC30" s="14" t="s">
         <v>127</v>
       </c>
       <c r="AD30" s="15"/>
       <c r="AE30" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AF30" s="33" t="s">
+      <c r="AF30" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AG30" s="33"/>
-      <c r="AH30" s="33" t="s">
+      <c r="AG30" s="14"/>
+      <c r="AH30" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AI30" s="33" t="s">
+      <c r="AI30" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AJ30" s="33" t="s">
+      <c r="AJ30" s="14" t="s">
         <v>50</v>
       </c>
       <c r="AK30" s="15"/>
@@ -6040,18 +6083,18 @@
         <v>64</v>
       </c>
       <c r="C31" s="13"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="15"/>
       <c r="J31" s="13"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
       <c r="P31" s="15"/>
       <c r="Q31" s="13" t="s">
         <v>44</v>
@@ -6063,18 +6106,18 @@
       <c r="V31" s="14"/>
       <c r="W31" s="15"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="33"/>
-      <c r="Z31" s="33"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
-      <c r="AC31" s="33"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
       <c r="AD31" s="15"/>
       <c r="AE31" s="13"/>
-      <c r="AF31" s="33"/>
-      <c r="AG31" s="33"/>
-      <c r="AH31" s="33"/>
-      <c r="AI31" s="33"/>
-      <c r="AJ31" s="33"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="14"/>
+      <c r="AH31" s="14"/>
+      <c r="AI31" s="14"/>
+      <c r="AJ31" s="14"/>
       <c r="AK31" s="15"/>
     </row>
     <row r="32" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6087,34 +6130,34 @@
       <c r="C32" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33" t="s">
+      <c r="E32" s="14"/>
+      <c r="F32" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G32" s="33" t="s">
+      <c r="G32" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H32" s="33" t="s">
+      <c r="H32" s="14" t="s">
         <v>140</v>
       </c>
       <c r="I32" s="15"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="33" t="s">
+      <c r="K32" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="L32" s="33" t="s">
+      <c r="L32" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="M32" s="33" t="s">
+      <c r="M32" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="N32" s="33" t="s">
+      <c r="N32" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="O32" s="33" t="s">
+      <c r="O32" s="14" t="s">
         <v>140</v>
       </c>
       <c r="P32" s="15"/>
@@ -6136,28 +6179,30 @@
         <v>35</v>
       </c>
       <c r="X32" s="13"/>
-      <c r="Y32" s="33"/>
-      <c r="Z32" s="33"/>
-      <c r="AA32" s="33"/>
-      <c r="AB32" s="33" t="s">
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB32" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="AC32" s="33" t="s">
+      <c r="AC32" s="14" t="s">
         <v>44</v>
       </c>
       <c r="AD32" s="15" t="s">
         <v>46</v>
       </c>
       <c r="AE32" s="13"/>
-      <c r="AF32" s="33"/>
-      <c r="AG32" s="33" t="s">
+      <c r="AF32" s="14"/>
+      <c r="AG32" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="AH32" s="33" t="s">
+      <c r="AH32" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AI32" s="33"/>
-      <c r="AJ32" s="33" t="s">
+      <c r="AI32" s="14"/>
+      <c r="AJ32" s="14" t="s">
         <v>139</v>
       </c>
       <c r="AK32" s="15" t="s">
@@ -6172,30 +6217,30 @@
         <v>27</v>
       </c>
       <c r="C33" s="13"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33" t="s">
+      <c r="D33" s="14"/>
+      <c r="E33" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="33" t="s">
+      <c r="G33" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="33" t="s">
+      <c r="H33" s="14" t="s">
         <v>140</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>129</v>
       </c>
       <c r="J33" s="13"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33" t="s">
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="O33" s="33" t="s">
+      <c r="O33" s="14" t="s">
         <v>140</v>
       </c>
       <c r="P33" s="15"/>
@@ -6221,30 +6266,32 @@
       <c r="X33" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Y33" s="33" t="s">
+      <c r="Y33" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="Z33" s="33" t="s">
+      <c r="Z33" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AA33" s="33"/>
-      <c r="AB33" s="33"/>
-      <c r="AC33" s="33"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
       <c r="AD33" s="15"/>
       <c r="AE33" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AF33" s="33" t="s">
+      <c r="AF33" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AG33" s="33"/>
-      <c r="AH33" s="33" t="s">
+      <c r="AG33" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AI33" s="33" t="s">
+      <c r="AI33" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="AJ33" s="33" t="s">
+      <c r="AJ33" s="14" t="s">
         <v>139</v>
       </c>
       <c r="AK33" s="15"/>
@@ -6257,20 +6304,20 @@
         <v>65</v>
       </c>
       <c r="C34" s="13"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="15"/>
       <c r="J34" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
       <c r="P34" s="15"/>
       <c r="Q34" s="13"/>
       <c r="R34" s="14"/>
@@ -6280,18 +6327,18 @@
       <c r="V34" s="14"/>
       <c r="W34" s="14"/>
       <c r="X34" s="13"/>
-      <c r="Y34" s="33"/>
-      <c r="Z34" s="33"/>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
       <c r="AD34" s="15"/>
       <c r="AE34" s="13"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="14"/>
+      <c r="AH34" s="14"/>
+      <c r="AI34" s="14"/>
+      <c r="AJ34" s="14"/>
       <c r="AK34" s="15"/>
     </row>
     <row r="35" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6304,32 +6351,34 @@
       <c r="C35" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33" t="s">
+      <c r="E35" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H35" s="33"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="15"/>
       <c r="J35" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K35" s="33" t="s">
+      <c r="K35" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L35" s="33" t="s">
+      <c r="L35" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="M35" s="33" t="s">
+      <c r="M35" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
       <c r="P35" s="15"/>
       <c r="Q35" s="13" t="s">
         <v>46</v>
@@ -6351,32 +6400,32 @@
       </c>
       <c r="W35" s="15"/>
       <c r="X35" s="13"/>
-      <c r="Y35" s="33"/>
-      <c r="Z35" s="33"/>
-      <c r="AA35" s="33"/>
-      <c r="AB35" s="33" t="s">
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AC35" s="33" t="s">
+      <c r="AC35" s="14" t="s">
         <v>51</v>
       </c>
       <c r="AD35" s="15"/>
       <c r="AE35" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AF35" s="33" t="s">
+      <c r="AF35" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AG35" s="33" t="s">
+      <c r="AG35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AH35" s="33" t="s">
+      <c r="AH35" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AI35" s="33" t="s">
+      <c r="AI35" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AJ35" s="33" t="s">
+      <c r="AJ35" s="14" t="s">
         <v>127</v>
       </c>
       <c r="AK35" s="15"/>
@@ -6391,36 +6440,36 @@
       <c r="C36" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="D36" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33" t="s">
+      <c r="E36" s="14"/>
+      <c r="F36" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="33" t="s">
+      <c r="H36" s="14" t="s">
         <v>141</v>
       </c>
       <c r="I36" s="15"/>
       <c r="J36" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K36" s="33" t="s">
+      <c r="K36" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="L36" s="33" t="s">
+      <c r="L36" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="33" t="s">
+      <c r="M36" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="N36" s="33" t="s">
+      <c r="N36" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O36" s="33" t="s">
+      <c r="O36" s="14" t="s">
         <v>48</v>
       </c>
       <c r="P36" s="15"/>
@@ -6446,26 +6495,26 @@
       <c r="X36" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="Y36" s="33" t="s">
+      <c r="Y36" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="Z36" s="33" t="s">
+      <c r="Z36" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AA36" s="33" t="s">
+      <c r="AA36" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
       <c r="AD36" s="15"/>
       <c r="AE36" s="13"/>
-      <c r="AF36" s="33"/>
-      <c r="AG36" s="33"/>
-      <c r="AH36" s="33"/>
-      <c r="AI36" s="33" t="s">
+      <c r="AF36" s="14"/>
+      <c r="AG36" s="14"/>
+      <c r="AH36" s="14"/>
+      <c r="AI36" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="AJ36" s="33" t="s">
+      <c r="AJ36" s="14" t="s">
         <v>127</v>
       </c>
       <c r="AK36" s="15"/>
@@ -6478,20 +6527,20 @@
         <v>121</v>
       </c>
       <c r="C37" s="13"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
       <c r="I37" s="15"/>
       <c r="J37" s="13"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33" t="s">
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O37" s="33" t="s">
+      <c r="O37" s="14" t="s">
         <v>48</v>
       </c>
       <c r="P37" s="15"/>
@@ -6505,28 +6554,28 @@
       <c r="X37" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="Y37" s="33" t="s">
+      <c r="Y37" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="Z37" s="33" t="s">
+      <c r="Z37" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AA37" s="33" t="s">
+      <c r="AA37" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AB37" s="33" t="s">
+      <c r="AB37" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AC37" s="33" t="s">
+      <c r="AC37" s="14" t="s">
         <v>51</v>
       </c>
       <c r="AD37" s="15"/>
       <c r="AE37" s="13"/>
-      <c r="AF37" s="33"/>
-      <c r="AG37" s="33"/>
-      <c r="AH37" s="33"/>
-      <c r="AI37" s="33"/>
-      <c r="AJ37" s="33"/>
+      <c r="AF37" s="14"/>
+      <c r="AG37" s="14"/>
+      <c r="AH37" s="14"/>
+      <c r="AI37" s="14"/>
+      <c r="AJ37" s="14"/>
       <c r="AK37" s="15"/>
     </row>
     <row r="38" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6537,18 +6586,16 @@
         <v>142</v>
       </c>
       <c r="C38" s="13"/>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
       <c r="I38" s="15"/>
       <c r="J38" s="13"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="33"/>
-      <c r="M38" s="33"/>
-      <c r="N38" s="34"/>
-      <c r="O38" s="34"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
       <c r="P38" s="15"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="14"/>
@@ -6558,26 +6605,24 @@
       <c r="V38" s="14"/>
       <c r="W38" s="15"/>
       <c r="X38" s="13"/>
-      <c r="Y38" s="33"/>
-      <c r="Z38" s="33"/>
-      <c r="AA38" s="33"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
+      <c r="Y38" s="14"/>
+      <c r="Z38" s="14"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
       <c r="AD38" s="15"/>
       <c r="AE38" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AF38" s="33" t="s">
+      <c r="AF38" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="AG38" s="33" t="s">
+      <c r="AG38" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AH38" s="33" t="s">
+      <c r="AH38" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="AI38" s="35"/>
-      <c r="AJ38" s="35"/>
       <c r="AK38" s="15"/>
     </row>
     <row r="39" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6588,26 +6633,26 @@
         <v>30</v>
       </c>
       <c r="C39" s="13"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
       <c r="I39" s="15"/>
       <c r="J39" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K39" s="33" t="s">
+      <c r="K39" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="L39" s="33" t="s">
+      <c r="L39" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="33" t="s">
+      <c r="M39" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
+      <c r="N39" s="14"/>
+      <c r="O39" s="14"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="14"/>
@@ -6619,28 +6664,28 @@
       <c r="X39" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Y39" s="33" t="s">
+      <c r="Y39" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="Z39" s="33" t="s">
+      <c r="Z39" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AA39" s="33" t="s">
+      <c r="AA39" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33" t="s">
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AD39" s="15" t="s">
         <v>44</v>
       </c>
       <c r="AE39" s="13"/>
-      <c r="AF39" s="33"/>
-      <c r="AG39" s="33"/>
-      <c r="AH39" s="33"/>
-      <c r="AI39" s="33"/>
-      <c r="AJ39" s="33"/>
+      <c r="AF39" s="14"/>
+      <c r="AG39" s="14"/>
+      <c r="AH39" s="14"/>
+      <c r="AI39" s="14"/>
+      <c r="AJ39" s="14"/>
       <c r="AK39" s="15"/>
     </row>
     <row r="40" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6651,26 +6696,26 @@
         <v>31</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
       <c r="I40" s="15"/>
       <c r="J40" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="33" t="s">
+      <c r="K40" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="L40" s="33" t="s">
+      <c r="L40" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33" t="s">
+      <c r="M40" s="14"/>
+      <c r="N40" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="O40" s="33" t="s">
+      <c r="O40" s="14" t="s">
         <v>129</v>
       </c>
       <c r="P40" s="15" t="s">
@@ -6684,26 +6729,26 @@
       <c r="V40" s="14"/>
       <c r="W40" s="15"/>
       <c r="X40" s="13"/>
-      <c r="Y40" s="33"/>
-      <c r="Z40" s="33"/>
-      <c r="AA40" s="33" t="s">
+      <c r="Y40" s="14"/>
+      <c r="Z40" s="14"/>
+      <c r="AA40" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AB40" s="33" t="s">
+      <c r="AB40" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AC40" s="33" t="s">
+      <c r="AC40" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AD40" s="15" t="s">
         <v>44</v>
       </c>
       <c r="AE40" s="13"/>
-      <c r="AF40" s="33"/>
-      <c r="AG40" s="33"/>
-      <c r="AH40" s="33"/>
-      <c r="AI40" s="33"/>
-      <c r="AJ40" s="33"/>
+      <c r="AF40" s="14"/>
+      <c r="AG40" s="14"/>
+      <c r="AH40" s="14"/>
+      <c r="AI40" s="14"/>
+      <c r="AJ40" s="14"/>
       <c r="AK40" s="15"/>
     </row>
     <row r="41" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6714,22 +6759,22 @@
         <v>49</v>
       </c>
       <c r="C41" s="13"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
       <c r="I41" s="15"/>
       <c r="J41" s="13"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33" t="s">
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="N41" s="33" t="s">
+      <c r="N41" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="O41" s="33" t="s">
+      <c r="O41" s="14" t="s">
         <v>129</v>
       </c>
       <c r="P41" s="15" t="s">
@@ -6745,24 +6790,24 @@
       <c r="X41" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Y41" s="33" t="s">
+      <c r="Y41" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="Z41" s="33" t="s">
+      <c r="Z41" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="AA41" s="33"/>
-      <c r="AB41" s="33" t="s">
+      <c r="AA41" s="14"/>
+      <c r="AB41" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AC41" s="33"/>
+      <c r="AC41" s="14"/>
       <c r="AD41" s="15"/>
       <c r="AE41" s="13"/>
-      <c r="AF41" s="33"/>
-      <c r="AG41" s="33"/>
-      <c r="AH41" s="33"/>
-      <c r="AI41" s="33"/>
-      <c r="AJ41" s="33"/>
+      <c r="AF41" s="14"/>
+      <c r="AG41" s="14"/>
+      <c r="AH41" s="14"/>
+      <c r="AI41" s="14"/>
+      <c r="AJ41" s="14"/>
       <c r="AK41" s="15"/>
     </row>
     <row r="42" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6773,22 +6818,22 @@
         <v>32</v>
       </c>
       <c r="C42" s="13"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33" t="s">
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14" t="s">
         <v>37</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>44</v>
       </c>
       <c r="J42" s="13"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14"/>
       <c r="P42" s="15"/>
       <c r="Q42" s="13"/>
       <c r="R42" s="14"/>
@@ -6804,18 +6849,18 @@
         <v>38</v>
       </c>
       <c r="X42" s="13"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
-      <c r="AA42" s="33"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
+      <c r="Y42" s="14"/>
+      <c r="Z42" s="14"/>
+      <c r="AA42" s="14"/>
+      <c r="AB42" s="14"/>
+      <c r="AC42" s="14"/>
       <c r="AD42" s="15"/>
       <c r="AE42" s="13"/>
-      <c r="AF42" s="33"/>
-      <c r="AG42" s="33"/>
-      <c r="AH42" s="33"/>
-      <c r="AI42" s="33"/>
-      <c r="AJ42" s="33" t="s">
+      <c r="AF42" s="14"/>
+      <c r="AG42" s="14"/>
+      <c r="AH42" s="14"/>
+      <c r="AI42" s="14"/>
+      <c r="AJ42" s="14" t="s">
         <v>47</v>
       </c>
       <c r="AK42" s="15" t="s">

--- a/Raspored.xlsx
+++ b/Raspored.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\raspored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD30EE25-31F4-4E64-8BB4-0150AADF1BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C94B57-DEE8-47BD-B41A-EDDA01C962F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E29FE33D-0FD8-4EFA-99F6-035E72B381D0}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="162">
   <si>
     <t>ПОНЕДЕЉАК</t>
   </si>
@@ -527,6 +527,9 @@
   </si>
   <si>
     <t>6/6 ч</t>
+  </si>
+  <si>
+    <t>Бојана Камберовић</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1458,9 @@
       <c r="E4" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="14"/>
+      <c r="F4" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="G4" s="14" t="s">
         <v>73</v>
       </c>
@@ -1680,7 +1685,9 @@
       <c r="M7" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="N7" s="14"/>
+      <c r="N7" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="O7" s="14" t="s">
         <v>102</v>
       </c>
@@ -1767,7 +1774,9 @@
       </c>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
+      <c r="V8" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="W8" s="15"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="14"/>
@@ -1823,7 +1832,9 @@
       <c r="AB9" s="14"/>
       <c r="AC9" s="14"/>
       <c r="AD9" s="15"/>
-      <c r="AE9" s="13"/>
+      <c r="AE9" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AF9" s="14"/>
       <c r="AG9" s="14"/>
       <c r="AH9" s="14" t="s">
@@ -2232,7 +2243,9 @@
       <c r="Y15" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="Z15" s="14"/>
+      <c r="Z15" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AA15" s="14" t="s">
         <v>74</v>
       </c>
@@ -2669,7 +2682,9 @@
       <c r="E22" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="14"/>
+      <c r="F22" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
       <c r="I22" s="15"/>
@@ -2737,7 +2752,9 @@
       <c r="L23" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="M23" s="14"/>
+      <c r="M23" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="N23" s="14" t="s">
         <v>74</v>
       </c>
@@ -2817,7 +2834,9 @@
       <c r="M24" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="N24" s="14"/>
+      <c r="N24" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="O24" s="14"/>
       <c r="P24" s="15"/>
       <c r="Q24" s="13"/>
@@ -2998,7 +3017,9 @@
       <c r="E27" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F27" s="14"/>
+      <c r="F27" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15"/>
@@ -3046,7 +3067,9 @@
       <c r="F28" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="G28" s="14"/>
+      <c r="G28" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="H28" s="14" t="s">
         <v>76</v>
       </c>
@@ -3301,7 +3324,9 @@
       <c r="AH31" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="AI31" s="14"/>
+      <c r="AI31" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AJ31" s="14" t="s">
         <v>111</v>
       </c>
@@ -3578,7 +3603,9 @@
       <c r="C35" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D35" s="14"/>
+      <c r="D35" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="E35" s="14" t="s">
         <v>72</v>
       </c>
@@ -3692,7 +3719,9 @@
       <c r="AF36" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="AG36" s="14"/>
+      <c r="AG36" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AH36" s="14" t="s">
         <v>99</v>
       </c>
@@ -3985,7 +4014,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3ECECC-CD92-4953-8B0E-37D5442915EE}">
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
@@ -4249,7 +4278,9 @@
       <c r="D4" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="F4" s="14" t="s">
         <v>51</v>
       </c>
@@ -4648,32 +4679,30 @@
       <c r="AJ9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AK9" s="15"/>
+      <c r="AK9" s="14" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="10" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
+        <v>161</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="14"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
+      <c r="G10" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="H10" s="14"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="13" t="s">
-        <v>131</v>
-      </c>
+      <c r="J10" s="13"/>
       <c r="K10" s="14"/>
-      <c r="L10" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="M10" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
       <c r="N10" s="14"/>
       <c r="O10" s="14"/>
       <c r="P10" s="15"/>
@@ -4687,15 +4716,9 @@
       <c r="X10" s="13"/>
       <c r="Y10" s="14"/>
       <c r="Z10" s="14"/>
-      <c r="AA10" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB10" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="AC10" s="14" t="s">
-        <v>131</v>
-      </c>
+      <c r="AA10" s="14"/>
+      <c r="AB10" s="14"/>
+      <c r="AC10" s="14"/>
       <c r="AD10" s="15"/>
       <c r="AE10" s="13"/>
       <c r="AF10" s="14"/>
@@ -4703,14 +4726,14 @@
       <c r="AH10" s="14"/>
       <c r="AI10" s="14"/>
       <c r="AJ10" s="14"/>
-      <c r="AK10" s="15"/>
+      <c r="AK10" s="14"/>
     </row>
     <row r="11" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="14"/>
@@ -4719,20 +4742,18 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="14"/>
+      <c r="J11" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14" t="s">
+        <v>132</v>
+      </c>
       <c r="M11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>36</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="14"/>
@@ -4741,20 +4762,18 @@
       <c r="U11" s="14"/>
       <c r="V11" s="14"/>
       <c r="W11" s="15"/>
-      <c r="X11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y11" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z11" s="14" t="s">
-        <v>36</v>
-      </c>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
       <c r="AA11" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
+        <v>43</v>
+      </c>
+      <c r="AB11" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="AC11" s="14" t="s">
+        <v>131</v>
+      </c>
       <c r="AD11" s="15"/>
       <c r="AE11" s="13"/>
       <c r="AF11" s="14"/>
@@ -4769,7 +4788,7 @@
         <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="14"/>
@@ -4779,16 +4798,18 @@
       <c r="H12" s="14"/>
       <c r="I12" s="15"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
+      <c r="K12" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="13"/>
@@ -4799,16 +4820,16 @@
       <c r="V12" s="14"/>
       <c r="W12" s="15"/>
       <c r="X12" s="13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="Y12" s="14" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="Z12" s="14" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="AA12" s="14" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="AB12" s="14"/>
       <c r="AC12" s="14"/>
@@ -4823,10 +4844,10 @@
     </row>
     <row r="13" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>13</v>
+        <v>80</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="C13" s="13"/>
       <c r="D13" s="14"/>
@@ -4837,15 +4858,15 @@
       <c r="I13" s="15"/>
       <c r="J13" s="13"/>
       <c r="K13" s="14"/>
-      <c r="L13" s="14" t="s">
-        <v>132</v>
-      </c>
+      <c r="L13" s="14"/>
       <c r="M13" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="N13" s="14"/>
+        <v>70</v>
+      </c>
+      <c r="N13" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="O13" s="14" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="13"/>
@@ -4855,17 +4876,19 @@
       <c r="U13" s="14"/>
       <c r="V13" s="14"/>
       <c r="W13" s="15"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="14"/>
+      <c r="X13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y13" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="Z13" s="14" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="AA13" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB13" s="14" t="s">
-        <v>132</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="AB13" s="14"/>
       <c r="AC13" s="14"/>
       <c r="AD13" s="15"/>
       <c r="AE13" s="13"/>
@@ -4881,7 +4904,7 @@
         <v>81</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="14"/>
@@ -4890,23 +4913,17 @@
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14"/>
       <c r="L14" s="14" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="N14" s="14" t="s">
-        <v>134</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="N14" s="14"/>
       <c r="O14" s="14" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="P14" s="15"/>
       <c r="Q14" s="13"/>
@@ -4916,24 +4933,18 @@
       <c r="U14" s="14"/>
       <c r="V14" s="14"/>
       <c r="W14" s="15"/>
-      <c r="X14" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y14" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="14"/>
       <c r="Z14" s="14" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="AA14" s="14" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="AB14" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="AC14" s="14" t="s">
-        <v>131</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="AC14" s="14"/>
       <c r="AD14" s="15"/>
       <c r="AE14" s="13"/>
       <c r="AF14" s="14"/>
@@ -4945,89 +4956,69 @@
     </row>
     <row r="15" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
       <c r="G15" s="14"/>
       <c r="H15" s="14"/>
       <c r="I15" s="15"/>
       <c r="J15" s="13" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="O15" s="14"/>
+        <v>134</v>
+      </c>
+      <c r="O15" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="P15" s="15"/>
-      <c r="Q15" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="S15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="T15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="U15" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="14"/>
+      <c r="S15" s="14"/>
+      <c r="T15" s="14"/>
+      <c r="U15" s="14"/>
       <c r="V15" s="14"/>
       <c r="W15" s="15"/>
       <c r="X15" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y15" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA15" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="Y15" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
+      <c r="AB15" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC15" s="14" t="s">
+        <v>131</v>
+      </c>
       <c r="AD15" s="15"/>
-      <c r="AE15" s="13" t="s">
-        <v>48</v>
-      </c>
+      <c r="AE15" s="13"/>
       <c r="AF15" s="14"/>
-      <c r="AG15" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AH15" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AJ15" s="14" t="s">
-        <v>95</v>
-      </c>
+      <c r="AG15" s="14"/>
+      <c r="AH15" s="14"/>
+      <c r="AI15" s="14"/>
+      <c r="AJ15" s="14"/>
       <c r="AK15" s="15"/>
     </row>
     <row r="16" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5035,84 +5026,86 @@
         <v>82</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>137</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="15"/>
       <c r="J16" s="13" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="N16" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="O16" s="14"/>
       <c r="P16" s="15"/>
       <c r="Q16" s="13" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="R16" s="14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="S16" s="14" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="U16" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V16" s="14"/>
       <c r="W16" s="15"/>
       <c r="X16" s="13" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="Y16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="Z16" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA16" s="14"/>
       <c r="AB16" s="14"/>
       <c r="AC16" s="14"/>
       <c r="AD16" s="15"/>
       <c r="AE16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF16" s="14" t="s">
-        <v>38</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="AF16" s="14"/>
       <c r="AG16" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AH16" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI16" s="14"/>
-      <c r="AJ16" s="14"/>
+        <v>35</v>
+      </c>
+      <c r="AI16" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AJ16" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="AK16" s="15"/>
     </row>
     <row r="17" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5120,59 +5113,85 @@
         <v>82</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+        <v>15</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="F17" s="14" t="s">
-        <v>50</v>
+        <v>154</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="14"/>
+        <v>37</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>137</v>
+      </c>
       <c r="I17" s="15"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
+      <c r="J17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="N17" s="14"/>
       <c r="O17" s="14"/>
       <c r="P17" s="15"/>
       <c r="Q17" s="13" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="R17" s="14" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="S17" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="U17" s="14"/>
+        <v>129</v>
+      </c>
+      <c r="U17" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="V17" s="14"/>
       <c r="W17" s="15"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="14"/>
+      <c r="X17" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y17" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
+      <c r="AA17" s="14" t="s">
+        <v>47</v>
+      </c>
       <c r="AB17" s="14"/>
       <c r="AC17" s="14"/>
       <c r="AD17" s="15"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="14"/>
+      <c r="AE17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF17" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="AG17" s="14" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AH17" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AI17" s="14" t="s">
-        <v>50</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="AI17" s="14"/>
       <c r="AJ17" s="14"/>
       <c r="AK17" s="15"/>
     </row>
@@ -5181,19 +5200,17 @@
         <v>82</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
+        <v>16</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="H18" s="14"/>
       <c r="I18" s="15"/>
       <c r="J18" s="13"/>
@@ -5203,278 +5220,256 @@
       <c r="N18" s="14"/>
       <c r="O18" s="14"/>
       <c r="P18" s="15"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
+      <c r="Q18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="R18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="U18" s="14"/>
       <c r="V18" s="14"/>
       <c r="W18" s="15"/>
-      <c r="X18" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z18" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
       <c r="AA18" s="14"/>
       <c r="AB18" s="14"/>
       <c r="AC18" s="14"/>
       <c r="AD18" s="15"/>
-      <c r="AE18" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF18" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG18" s="14"/>
-      <c r="AH18" s="14"/>
-      <c r="AI18" s="14"/>
+      <c r="AE18" s="13"/>
+      <c r="AF18" s="14"/>
+      <c r="AG18" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH18" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AI18" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="AJ18" s="14"/>
       <c r="AK18" s="15"/>
     </row>
     <row r="19" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
       <c r="I19" s="15"/>
-      <c r="J19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="L19" s="14" t="s">
-        <v>36</v>
-      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
       <c r="O19" s="14"/>
       <c r="P19" s="15"/>
-      <c r="Q19" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="R19" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="S19" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="T19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="U19" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="V19" s="14" t="s">
-        <v>129</v>
-      </c>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
       <c r="W19" s="15"/>
       <c r="X19" s="13" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="Y19" s="14" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="Z19" s="14" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="AA19" s="14"/>
       <c r="AB19" s="14"/>
       <c r="AC19" s="14"/>
       <c r="AD19" s="15"/>
       <c r="AE19" s="13" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="AF19" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG19" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AH19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AI19" s="14" t="s">
         <v>51</v>
       </c>
+      <c r="AG19" s="14"/>
+      <c r="AH19" s="14"/>
+      <c r="AI19" s="14"/>
       <c r="AJ19" s="14"/>
       <c r="AK19" s="15"/>
     </row>
     <row r="20" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>129</v>
-      </c>
       <c r="H20" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="K20" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
+      <c r="L20" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="M20" s="14"/>
       <c r="N20" s="14"/>
       <c r="O20" s="14"/>
       <c r="P20" s="15"/>
-      <c r="Q20" s="13"/>
+      <c r="Q20" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="R20" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="S20" s="14"/>
+        <v>138</v>
+      </c>
+      <c r="S20" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="T20" s="14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="U20" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="V20" s="14" t="s">
-        <v>46</v>
-      </c>
       <c r="W20" s="15"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
+      <c r="X20" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z20" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="AA20" s="14"/>
       <c r="AB20" s="14"/>
       <c r="AC20" s="14"/>
       <c r="AD20" s="15"/>
       <c r="AE20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF20" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG20" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH20" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AF20" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AG20" s="14" t="s">
+      <c r="AI20" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AH20" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI20" s="14"/>
       <c r="AJ20" s="14"/>
       <c r="AK20" s="15"/>
     </row>
     <row r="21" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>43</v>
-      </c>
       <c r="E21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+        <v>44</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="I21" s="15"/>
-      <c r="J21" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M21" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="J21" s="13"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
       <c r="P21" s="15"/>
       <c r="Q21" s="13"/>
-      <c r="R21" s="14"/>
+      <c r="R21" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="S21" s="14"/>
       <c r="T21" s="14" t="s">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="U21" s="14" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="V21" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W21" s="15"/>
-      <c r="X21" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y21" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z21" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA21" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB21" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC21" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
       <c r="AD21" s="15"/>
       <c r="AE21" s="13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AF21" s="14" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="AG21" s="14" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="AH21" s="14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AI21" s="14"/>
       <c r="AJ21" s="14"/>
@@ -5485,143 +5480,145 @@
         <v>85</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>51</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="15"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
+      <c r="J22" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="O22" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="P22" s="15"/>
-      <c r="Q22" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="R22" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="S22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="U22" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="V22" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="W22" s="15"/>
-      <c r="X22" s="13"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
+      <c r="X22" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z22" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA22" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB22" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC22" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="AD22" s="15"/>
-      <c r="AE22" s="13"/>
-      <c r="AF22" s="14"/>
-      <c r="AG22" s="14"/>
-      <c r="AH22" s="14"/>
-      <c r="AI22" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AJ22" s="14" t="s">
-        <v>37</v>
-      </c>
+      <c r="AE22" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF22" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG22" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH22" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI22" s="14"/>
+      <c r="AJ22" s="14"/>
       <c r="AK22" s="15"/>
     </row>
     <row r="23" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" s="13"/>
-      <c r="D23" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="14" t="s">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="G23" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="I23" s="15"/>
-      <c r="J23" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>47</v>
-      </c>
+      <c r="J23" s="13"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
       <c r="M23" s="14"/>
-      <c r="N23" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="O23" s="14" t="s">
-        <v>159</v>
-      </c>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
       <c r="P23" s="15"/>
       <c r="Q23" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="R23" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="S23" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="R23" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="S23" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="T23" s="14"/>
       <c r="U23" s="14"/>
       <c r="V23" s="14"/>
       <c r="W23" s="15"/>
-      <c r="X23" s="13" t="s">
+      <c r="X23" s="13"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="14"/>
+      <c r="AG23" s="14"/>
+      <c r="AH23" s="14"/>
+      <c r="AI23" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AJ23" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="Y23" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z23" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC23" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD23" s="15"/>
-      <c r="AE23" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG23" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AH23" s="14"/>
-      <c r="AI23" s="14"/>
-      <c r="AJ23" s="14"/>
       <c r="AK23" s="15"/>
     </row>
     <row r="24" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5629,55 +5626,91 @@
         <v>86</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="G24" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="14"/>
+        <v>51</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="I24" s="15"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
+      <c r="J24" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="O24" s="14" t="s">
+        <v>159</v>
+      </c>
       <c r="P24" s="15"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="Q24" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="R24" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="S24" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="T24" s="14"/>
       <c r="U24" s="14"/>
       <c r="V24" s="14"/>
       <c r="W24" s="15"/>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
+      <c r="X24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y24" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z24" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
+      <c r="AB24" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC24" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="AD24" s="15"/>
-      <c r="AE24" s="13"/>
-      <c r="AF24" s="14"/>
-      <c r="AG24" s="14"/>
-      <c r="AH24" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI24" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="AE24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AG24" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AH24" s="14"/>
+      <c r="AI24" s="14"/>
       <c r="AJ24" s="14"/>
       <c r="AK24" s="15"/>
     </row>
-    <row r="25" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>22</v>
@@ -5686,13 +5719,11 @@
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
       <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>134</v>
-      </c>
+      <c r="G25" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
       <c r="J25" s="13"/>
       <c r="K25" s="14"/>
       <c r="L25" s="14"/>
@@ -5701,18 +5732,14 @@
       <c r="O25" s="14"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="13"/>
-      <c r="R25" s="17"/>
-      <c r="S25" s="17"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="V25" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="W25" s="15" t="s">
-        <v>132</v>
-      </c>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="15"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="14"/>
       <c r="Z25" s="14"/>
@@ -5723,187 +5750,187 @@
       <c r="AE25" s="13"/>
       <c r="AF25" s="14"/>
       <c r="AG25" s="14"/>
-      <c r="AH25" s="14"/>
-      <c r="AI25" s="14"/>
-      <c r="AJ25" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="AK25" s="15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AH25" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI25" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ25" s="14"/>
+      <c r="AK25" s="15"/>
+    </row>
+    <row r="26" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>35</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="13" t="s">
+      <c r="H26" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="I26" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="13"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
       <c r="M26" s="14"/>
-      <c r="N26" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="O26" s="14" t="s">
-        <v>46</v>
-      </c>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
       <c r="P26" s="15"/>
-      <c r="Q26" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="R26" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="S26" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="T26" s="14" t="s">
-        <v>154</v>
-      </c>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="17"/>
+      <c r="T26" s="14"/>
       <c r="U26" s="14" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="V26" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="W26" s="15"/>
+        <v>147</v>
+      </c>
+      <c r="W26" s="15" t="s">
+        <v>132</v>
+      </c>
       <c r="X26" s="13"/>
       <c r="Y26" s="14"/>
-      <c r="Z26" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA26" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB26" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC26" s="14" t="s">
-        <v>129</v>
-      </c>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
       <c r="AD26" s="15"/>
-      <c r="AE26" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AF26" s="14" t="s">
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="14"/>
+      <c r="AH26" s="14"/>
+      <c r="AI26" s="14"/>
+      <c r="AJ26" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="AK26" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AG26" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AH26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI26" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AJ26" s="14"/>
-      <c r="AK26" s="15"/>
     </row>
     <row r="27" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>87</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G27" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>48</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="15"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
+      <c r="J27" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
+      <c r="N27" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="O27" s="14" t="s">
+        <v>46</v>
+      </c>
       <c r="P27" s="15"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="14"/>
-      <c r="S27" s="14"/>
-      <c r="T27" s="14"/>
-      <c r="U27" s="14"/>
-      <c r="V27" s="14"/>
+      <c r="Q27" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R27" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="T27" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="U27" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="V27" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="W27" s="15"/>
       <c r="X27" s="13"/>
       <c r="Y27" s="14"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-      <c r="AB27" s="14"/>
-      <c r="AC27" s="14"/>
+      <c r="Z27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA27" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB27" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC27" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="AD27" s="15"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="14"/>
-      <c r="AG27" s="14"/>
-      <c r="AH27" s="14"/>
-      <c r="AI27" s="14"/>
+      <c r="AE27" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF27" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG27" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI27" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="AJ27" s="14"/>
       <c r="AK27" s="15"/>
     </row>
     <row r="28" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
+      <c r="H28" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="I28" s="15"/>
       <c r="J28" s="13"/>
       <c r="K28" s="14"/>
       <c r="L28" s="14"/>
-      <c r="M28" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="N28" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>43</v>
-      </c>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
       <c r="P28" s="15"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="14"/>
@@ -5912,27 +5939,13 @@
       <c r="U28" s="14"/>
       <c r="V28" s="14"/>
       <c r="W28" s="15"/>
-      <c r="X28" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y28" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z28" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA28" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB28" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AC28" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD28" s="15" t="s">
-        <v>50</v>
-      </c>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="15"/>
       <c r="AE28" s="13"/>
       <c r="AF28" s="14"/>
       <c r="AG28" s="14"/>
@@ -5946,21 +5959,35 @@
         <v>88</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+        <v>149</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="15"/>
       <c r="J29" s="13"/>
       <c r="K29" s="14"/>
       <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
+      <c r="M29" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="O29" s="14" t="s">
+        <v>43</v>
+      </c>
       <c r="P29" s="15"/>
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
@@ -5969,47 +5996,45 @@
       <c r="U29" s="14"/>
       <c r="V29" s="14"/>
       <c r="W29" s="15"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="14"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
-      <c r="AD29" s="15"/>
-      <c r="AE29" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF29" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="X29" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y29" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z29" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA29" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB29" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AC29" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD29" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="14"/>
       <c r="AG29" s="14"/>
-      <c r="AH29" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="AI29" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ29" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="AH29" s="14"/>
+      <c r="AI29" s="14"/>
+      <c r="AJ29" s="14"/>
       <c r="AK29" s="15"/>
     </row>
     <row r="30" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>129</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
       <c r="F30" s="14"/>
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
@@ -6018,60 +6043,40 @@
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
-      <c r="N30" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="O30" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="13"/>
       <c r="R30" s="14"/>
-      <c r="S30" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="U30" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="V30" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
       <c r="W30" s="15"/>
       <c r="X30" s="13"/>
-      <c r="Y30" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z30" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA30" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AB30" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC30" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
       <c r="AD30" s="15"/>
       <c r="AE30" s="13" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AF30" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG30" s="14"/>
+        <v>45</v>
+      </c>
+      <c r="AG30" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AH30" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AI30" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AJ30" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AK30" s="15"/>
     </row>
@@ -6080,11 +6085,17 @@
         <v>89</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+        <v>25</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>129</v>
+      </c>
       <c r="F31" s="14"/>
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
@@ -6093,150 +6104,142 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
+      <c r="N31" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="O31" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="P31" s="15"/>
-      <c r="Q31" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="Q31" s="13"/>
       <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
+      <c r="S31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="T31" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="U31" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="V31" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="W31" s="15"/>
       <c r="X31" s="13"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
+      <c r="Y31" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z31" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA31" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB31" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC31" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="AD31" s="15"/>
-      <c r="AE31" s="13"/>
-      <c r="AF31" s="14"/>
+      <c r="AE31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AF31" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="AG31" s="14"/>
-      <c r="AH31" s="14"/>
-      <c r="AI31" s="14"/>
-      <c r="AJ31" s="14"/>
+      <c r="AH31" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ31" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="AK31" s="15"/>
     </row>
     <row r="32" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>46</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="14"/>
       <c r="E32" s="14"/>
-      <c r="F32" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>140</v>
-      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
       <c r="I32" s="15"/>
       <c r="J32" s="13"/>
-      <c r="K32" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="L32" s="14" t="s">
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="M32" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N32" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="O32" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="13"/>
       <c r="R32" s="14"/>
-      <c r="S32" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="T32" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="U32" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="V32" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="W32" s="14" t="s">
-        <v>35</v>
-      </c>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="15"/>
       <c r="X32" s="13"/>
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
-      <c r="AA32" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB32" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="AC32" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD32" s="15" t="s">
-        <v>46</v>
-      </c>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="15"/>
       <c r="AE32" s="13"/>
       <c r="AF32" s="14"/>
-      <c r="AG32" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH32" s="14" t="s">
-        <v>69</v>
-      </c>
+      <c r="AG32" s="14"/>
+      <c r="AH32" s="14"/>
       <c r="AI32" s="14"/>
-      <c r="AJ32" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="AK32" s="15" t="s">
-        <v>51</v>
-      </c>
+      <c r="AJ32" s="14"/>
+      <c r="AK32" s="15"/>
     </row>
     <row r="33" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="14"/>
       <c r="F33" s="14" t="s">
         <v>139</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>155</v>
+        <v>44</v>
       </c>
       <c r="H33" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I33" s="15" t="s">
-        <v>129</v>
-      </c>
+      <c r="I33" s="15"/>
       <c r="J33" s="13"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
+      <c r="K33" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="N33" s="14" t="s">
         <v>69</v>
       </c>
@@ -6244,12 +6247,8 @@
         <v>140</v>
       </c>
       <c r="P33" s="15"/>
-      <c r="Q33" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="R33" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="14"/>
       <c r="S33" s="14" t="s">
         <v>140</v>
       </c>
@@ -6257,177 +6256,175 @@
         <v>139</v>
       </c>
       <c r="U33" s="14" t="s">
-        <v>50</v>
+        <v>157</v>
       </c>
       <c r="V33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="W33" s="14"/>
-      <c r="X33" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y33" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z33" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="15"/>
-      <c r="AE33" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF33" s="14" t="s">
-        <v>47</v>
-      </c>
+      <c r="W33" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB33" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC33" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE33" s="13"/>
+      <c r="AF33" s="14"/>
       <c r="AG33" s="14" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="AH33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AI33" s="14" t="s">
-        <v>38</v>
-      </c>
+      <c r="AI33" s="14"/>
       <c r="AJ33" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="AK33" s="15"/>
+      <c r="AK33" s="15" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="34" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C34" s="13"/>
       <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="13" t="s">
-        <v>50</v>
-      </c>
+      <c r="E34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I34" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="J34" s="13"/>
       <c r="K34" s="14"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
+      <c r="N34" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34" s="14" t="s">
+        <v>140</v>
+      </c>
       <c r="P34" s="15"/>
-      <c r="Q34" s="13"/>
-      <c r="R34" s="14"/>
-      <c r="S34" s="14"/>
-      <c r="T34" s="14"/>
-      <c r="U34" s="14"/>
-      <c r="V34" s="14"/>
+      <c r="Q34" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="R34" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="T34" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="U34" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="V34" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="W34" s="14"/>
-      <c r="X34" s="13"/>
-      <c r="Y34" s="14"/>
-      <c r="Z34" s="14"/>
+      <c r="X34" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y34" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="Z34" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="AA34" s="14"/>
       <c r="AB34" s="14"/>
       <c r="AC34" s="14"/>
       <c r="AD34" s="15"/>
-      <c r="AE34" s="13"/>
-      <c r="AF34" s="14"/>
-      <c r="AG34" s="14"/>
-      <c r="AH34" s="14"/>
-      <c r="AI34" s="14"/>
-      <c r="AJ34" s="14"/>
+      <c r="AE34" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF34" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG34" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH34" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI34" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ34" s="14" t="s">
+        <v>139</v>
+      </c>
       <c r="AK34" s="15"/>
     </row>
     <row r="35" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>47</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="C35" s="13"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15"/>
       <c r="J35" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="L35" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="M35" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="15"/>
-      <c r="Q35" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="R35" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="S35" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="T35" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="U35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="V35" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="W35" s="15"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
       <c r="X35" s="13"/>
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="14"/>
-      <c r="AB35" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC35" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
       <c r="AD35" s="15"/>
-      <c r="AE35" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF35" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG35" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH35" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AI35" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="AJ35" s="14" t="s">
-        <v>127</v>
-      </c>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="14"/>
+      <c r="AH35" s="14"/>
+      <c r="AI35" s="14"/>
+      <c r="AJ35" s="14"/>
       <c r="AK35" s="15"/>
     </row>
     <row r="36" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6435,7 +6432,7 @@
         <v>91</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>36</v>
@@ -6443,16 +6440,16 @@
       <c r="D36" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="14"/>
+      <c r="E36" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="F36" s="14" t="s">
         <v>47</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="H36" s="14" t="s">
-        <v>141</v>
-      </c>
+      <c r="H36" s="14"/>
       <c r="I36" s="15"/>
       <c r="J36" s="13" t="s">
         <v>44</v>
@@ -6466,12 +6463,8 @@
       <c r="M36" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="N36" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="O36" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
       <c r="P36" s="15"/>
       <c r="Q36" s="13" t="s">
         <v>46</v>
@@ -6492,25 +6485,29 @@
         <v>35</v>
       </c>
       <c r="W36" s="15"/>
-      <c r="X36" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y36" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z36" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA36" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC36" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="AD36" s="15"/>
-      <c r="AE36" s="13"/>
-      <c r="AF36" s="14"/>
-      <c r="AG36" s="14"/>
-      <c r="AH36" s="14"/>
+      <c r="AE36" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG36" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH36" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="AI36" s="14" t="s">
         <v>127</v>
       </c>
@@ -6524,19 +6521,39 @@
         <v>91</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+        <v>29</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>141</v>
+      </c>
       <c r="I37" s="15"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
+      <c r="J37" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="N37" s="14" t="s">
         <v>48</v>
       </c>
@@ -6544,12 +6561,24 @@
         <v>48</v>
       </c>
       <c r="P37" s="15"/>
-      <c r="Q37" s="13"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
+      <c r="Q37" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="R37" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="S37" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="T37" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="U37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="V37" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="W37" s="15"/>
       <c r="X37" s="13" t="s">
         <v>38</v>
@@ -6563,19 +6592,19 @@
       <c r="AA37" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="AB37" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC37" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
       <c r="AD37" s="15"/>
       <c r="AE37" s="13"/>
       <c r="AF37" s="14"/>
       <c r="AG37" s="14"/>
       <c r="AH37" s="14"/>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
+      <c r="AI37" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="AJ37" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="AK37" s="15"/>
     </row>
     <row r="38" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6583,7 +6612,7 @@
         <v>91</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="C38" s="13"/>
       <c r="D38" s="14"/>
@@ -6596,6 +6625,12 @@
       <c r="K38" s="14"/>
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
+      <c r="N38" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="O38" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="P38" s="15"/>
       <c r="Q38" s="13"/>
       <c r="R38" s="14"/>
@@ -6604,33 +6639,39 @@
       <c r="U38" s="14"/>
       <c r="V38" s="14"/>
       <c r="W38" s="15"/>
-      <c r="X38" s="13"/>
-      <c r="Y38" s="14"/>
-      <c r="Z38" s="14"/>
-      <c r="AA38" s="14"/>
-      <c r="AB38" s="14"/>
-      <c r="AC38" s="14"/>
+      <c r="X38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y38" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z38" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA38" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB38" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AC38" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="AD38" s="15"/>
-      <c r="AE38" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF38" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="AG38" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH38" s="14" t="s">
-        <v>45</v>
-      </c>
+      <c r="AE38" s="13"/>
+      <c r="AF38" s="14"/>
+      <c r="AG38" s="14"/>
+      <c r="AH38" s="14"/>
+      <c r="AI38" s="14"/>
+      <c r="AJ38" s="14"/>
       <c r="AK38" s="15"/>
     </row>
     <row r="39" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>30</v>
+        <v>142</v>
       </c>
       <c r="C39" s="13"/>
       <c r="D39" s="14"/>
@@ -6639,20 +6680,10 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15"/>
-      <c r="J39" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="N39" s="14"/>
-      <c r="O39" s="14"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="14"/>
       <c r="P39" s="15"/>
       <c r="Q39" s="13"/>
       <c r="R39" s="14"/>
@@ -6661,31 +6692,28 @@
       <c r="U39" s="14"/>
       <c r="V39" s="14"/>
       <c r="W39" s="15"/>
-      <c r="X39" s="13" t="s">
+      <c r="X39" s="13"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="14"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="15"/>
+      <c r="AE39" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="Y39" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z39" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA39" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="AB39" s="14"/>
-      <c r="AC39" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD39" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="14"/>
-      <c r="AG39" s="14"/>
-      <c r="AH39" s="14"/>
-      <c r="AI39" s="14"/>
-      <c r="AJ39" s="14"/>
+      <c r="AF39" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH39" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI39" s="14" t="s">
+        <v>154</v>
+      </c>
       <c r="AK39" s="15"/>
     </row>
     <row r="40" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6693,7 +6721,7 @@
         <v>92</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C40" s="13"/>
       <c r="D40" s="14"/>
@@ -6711,16 +6739,12 @@
       <c r="L40" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="O40" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="P40" s="15" t="s">
-        <v>38</v>
-      </c>
+      <c r="M40" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="15"/>
       <c r="Q40" s="13"/>
       <c r="R40" s="14"/>
       <c r="S40" s="14"/>
@@ -6728,15 +6752,19 @@
       <c r="U40" s="14"/>
       <c r="V40" s="14"/>
       <c r="W40" s="15"/>
-      <c r="X40" s="13"/>
-      <c r="Y40" s="14"/>
-      <c r="Z40" s="14"/>
+      <c r="X40" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z40" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="AA40" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="AB40" s="14" t="s">
-        <v>50</v>
-      </c>
+      <c r="AB40" s="14"/>
       <c r="AC40" s="14" t="s">
         <v>36</v>
       </c>
@@ -6756,7 +6784,7 @@
         <v>92</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C41" s="13"/>
       <c r="D41" s="14"/>
@@ -6765,12 +6793,16 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14" t="s">
-        <v>51</v>
-      </c>
+      <c r="J41" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M41" s="14"/>
       <c r="N41" s="14" t="s">
         <v>46</v>
       </c>
@@ -6787,21 +6819,21 @@
       <c r="U41" s="14"/>
       <c r="V41" s="14"/>
       <c r="W41" s="15"/>
-      <c r="X41" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y41" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z41" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA41" s="14"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="14"/>
+      <c r="Z41" s="14"/>
+      <c r="AA41" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="AB41" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="AC41" s="14"/>
-      <c r="AD41" s="15"/>
+      <c r="AC41" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD41" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="AE41" s="13"/>
       <c r="AF41" s="14"/>
       <c r="AG41" s="14"/>
@@ -6812,47 +6844,53 @@
     </row>
     <row r="42" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B42" s="26" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C42" s="13"/>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
       <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>44</v>
-      </c>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15"/>
       <c r="J42" s="13"/>
       <c r="K42" s="14"/>
       <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="15"/>
+      <c r="M42" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="O42" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="P42" s="15" t="s">
+        <v>38</v>
+      </c>
       <c r="Q42" s="13"/>
       <c r="R42" s="14"/>
       <c r="S42" s="14"/>
       <c r="T42" s="14"/>
-      <c r="U42" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="V42" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="W42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X42" s="13"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
+      <c r="U42" s="14"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="15"/>
+      <c r="X42" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y42" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z42" s="14" t="s">
+        <v>48</v>
+      </c>
       <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
+      <c r="AB42" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="AC42" s="14"/>
       <c r="AD42" s="15"/>
       <c r="AE42" s="13"/>
@@ -6860,65 +6898,118 @@
       <c r="AG42" s="14"/>
       <c r="AH42" s="14"/>
       <c r="AI42" s="14"/>
-      <c r="AJ42" s="14" t="s">
+      <c r="AJ42" s="14"/>
+      <c r="AK42" s="15"/>
+    </row>
+    <row r="43" spans="1:37" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="13"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" s="13"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+      <c r="P43" s="15"/>
+      <c r="Q43" s="13"/>
+      <c r="R43" s="14"/>
+      <c r="S43" s="14"/>
+      <c r="T43" s="14"/>
+      <c r="U43" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="V43" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="W43" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="X43" s="13"/>
+      <c r="Y43" s="14"/>
+      <c r="Z43" s="14"/>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="14"/>
+      <c r="AD43" s="15"/>
+      <c r="AE43" s="13"/>
+      <c r="AF43" s="14"/>
+      <c r="AG43" s="14"/>
+      <c r="AH43" s="14"/>
+      <c r="AI43" s="14"/>
+      <c r="AJ43" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="AK42" s="15" t="s">
+      <c r="AK43" s="15" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="25" t="s">
+    <row r="44" spans="1:37" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B44" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="18" t="s">
+      <c r="C44" s="16"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
-      <c r="U43" s="17" t="s">
+      <c r="J44" s="16"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="16"/>
+      <c r="R44" s="17"/>
+      <c r="S44" s="17"/>
+      <c r="T44" s="17"/>
+      <c r="U44" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="V43" s="17" t="s">
+      <c r="V44" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="W43" s="18" t="s">
+      <c r="W44" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="X43" s="16"/>
-      <c r="Y43" s="17"/>
-      <c r="Z43" s="17"/>
-      <c r="AA43" s="17"/>
-      <c r="AB43" s="17"/>
-      <c r="AC43" s="17"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="16"/>
-      <c r="AF43" s="17"/>
-      <c r="AG43" s="17"/>
-      <c r="AH43" s="17"/>
-      <c r="AI43" s="17"/>
-      <c r="AJ43" s="17" t="s">
+      <c r="X44" s="16"/>
+      <c r="Y44" s="17"/>
+      <c r="Z44" s="17"/>
+      <c r="AA44" s="17"/>
+      <c r="AB44" s="17"/>
+      <c r="AC44" s="17"/>
+      <c r="AD44" s="18"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="17"/>
+      <c r="AG44" s="17"/>
+      <c r="AH44" s="17"/>
+      <c r="AI44" s="17"/>
+      <c r="AJ44" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="AK43" s="18" t="s">
+      <c r="AK44" s="18" t="s">
         <v>143</v>
       </c>
     </row>
